--- a/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
+++ b/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="Rcbc9c96c08db4c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="Ra4f2a63a9b8d4966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="R1682423bf02e443d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="R4522fae2c4a44cfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -415,22 +415,22 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="n">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="12" t="n">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C4" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="12" t="n">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>91</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F4" s="12" t="n">
-        <x:v>106434</x:v>
+        <x:v>171884</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -686,28 +686,28 @@
         <x:v>987839871</x:v>
       </x:c>
       <x:c r="J11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K11" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="L11" t="n">
-        <x:v>6925</x:v>
+        <x:v>9954</x:v>
       </x:c>
       <x:c r="M11" t="n">
-        <x:v>6925</x:v>
+        <x:v>9954</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>26/01/2026</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>05/06/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="P11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R11" t="n">
         <x:v>0</x:v>
@@ -851,28 +851,28 @@
         <x:v>51995736579</x:v>
       </x:c>
       <x:c r="J14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K14" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="L14" t="n">
-        <x:v>7014</x:v>
+        <x:v>8183</x:v>
       </x:c>
       <x:c r="M14" t="n">
-        <x:v>7014</x:v>
+        <x:v>8183</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>09/02/2026</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>20/06/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="P14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R14" t="n">
         <x:v>0</x:v>
@@ -1183,28 +1183,28 @@
         <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J20" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K20" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L20" t="n">
-        <x:v>1737</x:v>
+        <x:v>2895</x:v>
       </x:c>
       <x:c r="M20" t="n">
-        <x:v>1737</x:v>
+        <x:v>2895</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>12/03/2026</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="P20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R20" t="n">
         <x:v>0</x:v>
@@ -1411,28 +1411,28 @@
         <x:v>924699583</x:v>
       </x:c>
       <x:c r="J24" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K24" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L24" t="n">
-        <x:v>1937</x:v>
+        <x:v>3095</x:v>
       </x:c>
       <x:c r="M24" t="n">
-        <x:v>1937</x:v>
+        <x:v>3095</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>26/05/2026</x:v>
+        <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="P24" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R24" t="n">
         <x:v>0</x:v>
@@ -1639,28 +1639,28 @@
         <x:v>985773253</x:v>
       </x:c>
       <x:c r="J28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K28" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K28" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="L28" t="n">
-        <x:v>12905</x:v>
+        <x:v>15934</x:v>
       </x:c>
       <x:c r="M28" t="n">
-        <x:v>12905</x:v>
+        <x:v>15934</x:v>
       </x:c>
       <x:c r="N28" t="str">
         <x:v>06/04/2026</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>11/08/2026</x:v>
       </x:c>
       <x:c r="P28" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q28" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R28" t="n">
         <x:v>0</x:v>
@@ -1696,28 +1696,28 @@
         <x:v>51922218809</x:v>
       </x:c>
       <x:c r="J29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K29" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L29" t="n">
-        <x:v>6652</x:v>
+        <x:v>8871</x:v>
       </x:c>
       <x:c r="M29" t="n">
-        <x:v>6652</x:v>
+        <x:v>8871</x:v>
       </x:c>
       <x:c r="N29" t="str">
         <x:v>07/04/2026</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P29" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R29" t="n">
         <x:v>0</x:v>
@@ -1924,28 +1924,28 @@
         <x:v>962771928</x:v>
       </x:c>
       <x:c r="J33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K33" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L33" t="n">
-        <x:v>1989</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="M33" t="n">
-        <x:v>1989</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="N33" t="str">
         <x:v>24/04/2026</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>07/05/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="P33" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q33" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R33" t="n">
         <x:v>0</x:v>
@@ -2152,28 +2152,28 @@
         <x:v>51945678019</x:v>
       </x:c>
       <x:c r="J37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K37" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K37" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L37" t="n">
-        <x:v>2169</x:v>
+        <x:v>3338</x:v>
       </x:c>
       <x:c r="M37" t="n">
-        <x:v>2169</x:v>
+        <x:v>3338</x:v>
       </x:c>
       <x:c r="N37" t="str">
         <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R37" t="n">
         <x:v>0</x:v>
@@ -2209,28 +2209,28 @@
         <x:v>998119233</x:v>
       </x:c>
       <x:c r="J38" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K38" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L38" t="n">
-        <x:v>4438</x:v>
+        <x:v>7467</x:v>
       </x:c>
       <x:c r="M38" t="n">
-        <x:v>4438</x:v>
+        <x:v>7467</x:v>
       </x:c>
       <x:c r="N38" t="str">
         <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="P38" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R38" t="n">
         <x:v>0</x:v>
@@ -2323,28 +2323,28 @@
         <x:v>51951329266</x:v>
       </x:c>
       <x:c r="J40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K40" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L40" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="M40" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="N40" t="str">
         <x:v>29/05/2026</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>29/05/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="P40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R40" t="n">
         <x:v>0</x:v>
@@ -2380,28 +2380,28 @@
         <x:v>955098767</x:v>
       </x:c>
       <x:c r="J41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K41" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L41" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="M41" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="N41" t="str">
         <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="P41" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R41" t="n">
         <x:v>0</x:v>
@@ -2437,28 +2437,28 @@
         <x:v>51942126985</x:v>
       </x:c>
       <x:c r="J42" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K42" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L42" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="M42" t="n">
-        <x:v>1000</x:v>
+        <x:v>3219</x:v>
       </x:c>
       <x:c r="N42" t="str">
         <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P42" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q42" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R42" t="n">
         <x:v>0</x:v>
@@ -2551,28 +2551,28 @@
         <x:v>51945127771</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L44" t="n">
-        <x:v>1989</x:v>
+        <x:v>4147</x:v>
       </x:c>
       <x:c r="M44" t="n">
-        <x:v>1989</x:v>
+        <x:v>4147</x:v>
       </x:c>
       <x:c r="N44" t="str">
         <x:v>16/06/2026</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="P44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R44" t="n">
         <x:v>0</x:v>
@@ -2608,28 +2608,28 @@
         <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K45" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L45" t="n">
-        <x:v>1000</x:v>
+        <x:v>1989</x:v>
       </x:c>
       <x:c r="M45" t="n">
-        <x:v>1000</x:v>
+        <x:v>1989</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q45" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R45" t="n">
         <x:v>0</x:v>
@@ -2722,28 +2722,28 @@
         <x:v>51987504234</x:v>
       </x:c>
       <x:c r="J47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K47" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L47" t="n">
-        <x:v>1000</x:v>
+        <x:v>1779</x:v>
       </x:c>
       <x:c r="M47" t="n">
-        <x:v>1000</x:v>
+        <x:v>1779</x:v>
       </x:c>
       <x:c r="N47" t="str">
         <x:v>25/06/2026</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="P47" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q47" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R47" t="n">
         <x:v>0</x:v>
@@ -2779,28 +2779,28 @@
         <x:v>51969714361</x:v>
       </x:c>
       <x:c r="J48" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K48" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L48" t="n">
-        <x:v>1000</x:v>
+        <x:v>4029</x:v>
       </x:c>
       <x:c r="M48" t="n">
-        <x:v>1000</x:v>
+        <x:v>4029</x:v>
       </x:c>
       <x:c r="N48" t="str">
         <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="P48" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q48" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R48" t="n">
         <x:v>0</x:v>
@@ -2836,28 +2836,28 @@
         <x:v>51949429958</x:v>
       </x:c>
       <x:c r="J49" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K49" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L49" t="n">
-        <x:v>2219</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="M49" t="n">
-        <x:v>2219</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="N49" t="str">
         <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="P49" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q49" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R49" t="n">
         <x:v>0</x:v>
@@ -2920,6 +2920,910 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S50" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>999459492</x:v>
+      </x:c>
+      <x:c r="D51" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>10374186</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>999459492</x:v>
+      </x:c>
+      <x:c r="J51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="M51" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="N51" t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c r="O51" t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c r="P51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S51" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="D52" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>Web</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>76397222</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="J52" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L52" t="n">
+        <x:v>1779</x:v>
+      </x:c>
+      <x:c r="M52" t="n">
+        <x:v>1779</x:v>
+      </x:c>
+      <x:c r="N52" t="str">
+        <x:v>02/07/2026</x:v>
+      </x:c>
+      <x:c r="O52" t="str">
+        <x:v>15/07/2026</x:v>
+      </x:c>
+      <x:c r="P52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S52" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>Sve Chang</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>986185776</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>SVE CHANG</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>78007264</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>51 986 185 776</x:v>
+      </x:c>
+      <x:c r="J53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M53" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N53" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="O53" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="P53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S53" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>940219366</x:v>
+      </x:c>
+      <x:c r="D54" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>45267059</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>940 219 366</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L54" t="n">
+        <x:v>4438</x:v>
+      </x:c>
+      <x:c r="M54" t="n">
+        <x:v>4438</x:v>
+      </x:c>
+      <x:c r="N54" t="str">
+        <x:v>06/07/2026</x:v>
+      </x:c>
+      <x:c r="O54" t="str">
+        <x:v>03/08/2026</x:v>
+      </x:c>
+      <x:c r="P54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S54" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>941568528</x:v>
+      </x:c>
+      <x:c r="D55" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>009248655</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>51941568528</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L55" t="n">
+        <x:v>1579</x:v>
+      </x:c>
+      <x:c r="M55" t="n">
+        <x:v>1579</x:v>
+      </x:c>
+      <x:c r="N55" t="str">
+        <x:v>13/07/2026</x:v>
+      </x:c>
+      <x:c r="O55" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="P55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S55" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Marcela Noblecilla</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>998678319</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>10058157</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>51998 678 319</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M56" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N56" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="O56" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="P56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S56" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>992978868</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G57" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>09339021</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>51992978868</x:v>
+      </x:c>
+      <x:c r="J57" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L57" t="n">
+        <x:v>4119</x:v>
+      </x:c>
+      <x:c r="M57" t="n">
+        <x:v>4119</x:v>
+      </x:c>
+      <x:c r="N57" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="O57" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="P57" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>Jacqueline Idiaquez</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>997512348</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G58" t="str">
+        <x:v>Jacqueline Idiaquez</x:v>
+      </x:c>
+      <x:c r="H58" t="str">
+        <x:v>09673494</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>997 512 348</x:v>
+      </x:c>
+      <x:c r="J58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L58" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="M58" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="N58" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="O58" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="P58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>Lylian Leon</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>996500716</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G59" t="str">
+        <x:v>Lylian León</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>07619479</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>996500716</x:v>
+      </x:c>
+      <x:c r="J59" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M59" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N59" t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c r="O59" t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c r="P59" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>Karina Saavedra</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>984609397</x:v>
+      </x:c>
+      <x:c r="D60" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E60" t="str"/>
+      <x:c r="F60" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G60" t="str">
+        <x:v>Karina Saavedra Zarria</x:v>
+      </x:c>
+      <x:c r="H60" t="str">
+        <x:v>07628122</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>51984609397</x:v>
+      </x:c>
+      <x:c r="J60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M60" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N60" t="str">
+        <x:v>10/08/2026</x:v>
+      </x:c>
+      <x:c r="O60" t="str">
+        <x:v>10/08/2026</x:v>
+      </x:c>
+      <x:c r="P60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>977648321</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>40154559</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>51977648321</x:v>
+      </x:c>
+      <x:c r="J61" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L61" t="n">
+        <x:v>3285</x:v>
+      </x:c>
+      <x:c r="M61" t="n">
+        <x:v>3285</x:v>
+      </x:c>
+      <x:c r="N61" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="O61" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="P61" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>Jeanne Goncalvez</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>2022790015</x:v>
+      </x:c>
+      <x:c r="D62" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G62" t="str">
+        <x:v>JEANNE GONCALVEZ</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>20230943</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>51+1 (202) 279-0015</x:v>
+      </x:c>
+      <x:c r="J62" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L62" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M62" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N62" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O62" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P62" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G63" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M63" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N63" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O63" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>989174565</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="E64" t="str"/>
+      <x:c r="F64" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G64" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>09752091</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>51989174565</x:v>
+      </x:c>
+      <x:c r="J64" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="M64" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="N64" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O64" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P64" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>Maribel Toledo</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>949604263</x:v>
+      </x:c>
+      <x:c r="D65" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E65" t="str"/>
+      <x:c r="F65" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G65" t="str">
+        <x:v>MARIBEL TOLEDO</x:v>
+      </x:c>
+      <x:c r="H65" t="str">
+        <x:v>10477277</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>51949604263</x:v>
+      </x:c>
+      <x:c r="J65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L65" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M65" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N65" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O65" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="D66" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E66" t="str"/>
+      <x:c r="F66" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>10545751</x:v>
+      </x:c>
+      <x:c r="J66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L66" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M66" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N66" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="O66" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="P66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S66" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3626,11 +4530,11 @@
         <x:v>Enero 2026</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>Gabriela Prendes</x:v>
+        <x:v>Eduardo Añaños</x:v>
       </x:c>
       <x:c r="C12" t="str"/>
       <x:c r="D12" t="n">
-        <x:v>80</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E12" t="str">
         <x:v>Form web</x:v>
@@ -3639,79 +4543,79 @@
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>Gabriela Prendes Gonzales</x:v>
+        <x:v>Eduardo Añaños Gamarra</x:v>
       </x:c>
       <x:c r="H12" t="str">
-        <x:v>PAV714598</x:v>
+        <x:v>75056788</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>34600421821</x:v>
+        <x:v>987839871</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>30/01/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>30/01/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>31/01/2026</x:v>
+        <x:v>01/08/2026</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>80</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R12" t="n">
-        <x:v>80</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T12" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>Febrero 2026</x:v>
+        <x:v>Enero 2026</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>Ruben Rivera</x:v>
+        <x:v>Gabriela Prendes</x:v>
       </x:c>
       <x:c r="C13" t="str"/>
       <x:c r="D13" t="n">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E13" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form web</x:v>
       </x:c>
       <x:c r="F13" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>Ruben Rivera</x:v>
+        <x:v>Gabriela Prendes Gonzales</x:v>
       </x:c>
       <x:c r="H13" t="str">
-        <x:v>06383181</x:v>
+        <x:v>PAV714598</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>12124959986</x:v>
+        <x:v>34600421821</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L13" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -3720,25 +4624,25 @@
         <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>03/02/2026</x:v>
+        <x:v>30/01/2026</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>03/02/2026</x:v>
+        <x:v>30/01/2026</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>04/02/2026</x:v>
+        <x:v>31/01/2026</x:v>
       </x:c>
       <x:c r="Q13" t="n">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R13" t="n">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S13" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T13" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3768,10 +4672,10 @@
         <x:v>12124959986</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L14" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -3798,7 +4702,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T14" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3806,53 +4710,53 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>Franco Lizarraga</x:v>
+        <x:v>Ruben Rivera</x:v>
       </x:c>
       <x:c r="C15" t="str"/>
       <x:c r="D15" t="n">
-        <x:v>1169</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>Form meta</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F15" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>Franco Jaime Lizarraga</x:v>
+        <x:v>Ruben Rivera</x:v>
       </x:c>
       <x:c r="H15" t="str">
-        <x:v>4053750</x:v>
+        <x:v>06383181</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>51995736579</x:v>
+        <x:v>12124959986</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>09/02/2026</x:v>
+        <x:v>03/02/2026</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>10/02/2026</x:v>
+        <x:v>03/02/2026</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>13/03/2026</x:v>
+        <x:v>04/02/2026</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>1169</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="R15" t="n">
-        <x:v>1169</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="S15" t="n">
         <x:v>0</x:v>
@@ -3888,7 +4792,7 @@
         <x:v>51995736579</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K16" t="str">
         <x:v>Walk in</x:v>
@@ -3900,13 +4804,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>14/03/2026</x:v>
+        <x:v>09/02/2026</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>16/03/2026</x:v>
+        <x:v>10/02/2026</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>20/04/2026</x:v>
+        <x:v>13/03/2026</x:v>
       </x:c>
       <x:c r="Q16" t="n">
         <x:v>1169</x:v>
@@ -3918,7 +4822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T16" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3960,13 +4864,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>21/04/2026</x:v>
+        <x:v>14/03/2026</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>21/04/2026</x:v>
+        <x:v>16/03/2026</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>22/05/2026</x:v>
+        <x:v>20/04/2026</x:v>
       </x:c>
       <x:c r="Q17" t="n">
         <x:v>1169</x:v>
@@ -4011,7 +4915,7 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L18" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4020,13 +4924,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>28/05/2026</x:v>
+        <x:v>21/04/2026</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>28/05/2026</x:v>
+        <x:v>21/04/2026</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>22/05/2026</x:v>
       </x:c>
       <x:c r="Q18" t="n">
         <x:v>1169</x:v>
@@ -4080,13 +4984,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>20/06/2026</x:v>
+        <x:v>28/05/2026</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>20/06/2026</x:v>
+        <x:v>28/05/2026</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="Q19" t="n">
         <x:v>1169</x:v>
@@ -4131,7 +5035,7 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4143,10 +5047,10 @@
         <x:v>20/06/2026</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>20/06/2026</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>26/07/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="Q20" t="n">
         <x:v>1169</x:v>
@@ -4166,59 +5070,59 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>Alejandra Melendez</x:v>
+        <x:v>Franco Lizarraga</x:v>
       </x:c>
       <x:c r="C21" t="str"/>
       <x:c r="D21" t="n">
-        <x:v>859</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form meta</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>Alejandra Melendez</x:v>
+        <x:v>Franco Jaime Lizarraga</x:v>
       </x:c>
       <x:c r="H21" t="str">
-        <x:v>45938079</x:v>
+        <x:v>4053750</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>997037652</x:v>
+        <x:v>51995736579</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>12/02/2026</x:v>
+        <x:v>20/06/2026</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>12/02/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>13/02/2026</x:v>
+        <x:v>26/07/2026</x:v>
       </x:c>
       <x:c r="Q21" t="n">
-        <x:v>80</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R21" t="n">
-        <x:v>80</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S21" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T21" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4226,29 +5130,29 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>Alejandra Melendez</x:v>
+        <x:v>Franco Lizarraga</x:v>
       </x:c>
       <x:c r="C22" t="str"/>
       <x:c r="D22" t="n">
-        <x:v>859</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form meta</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>Alejandra Melendez</x:v>
+        <x:v>Franco Jaime Lizarraga</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>45938079</x:v>
+        <x:v>4053750</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>997037652</x:v>
+        <x:v>51995736579</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K22" t="str">
         <x:v>Walk in</x:v>
@@ -4260,25 +5164,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>14/02/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>20/02/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>22/03/2026</x:v>
+        <x:v>03/09/2026</x:v>
       </x:c>
       <x:c r="Q22" t="n">
-        <x:v>779</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R22" t="n">
-        <x:v>779</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S22" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T22" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4286,59 +5190,59 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>Yessica Flores</x:v>
+        <x:v>Alejandra Melendez</x:v>
       </x:c>
       <x:c r="C23" t="str"/>
       <x:c r="D23" t="n">
-        <x:v>150</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F23" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>YESSICA FLORES CAMBORDA</x:v>
+        <x:v>Alejandra Melendez</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>10263253</x:v>
+        <x:v>45938079</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>51998334629</x:v>
+        <x:v>997037652</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>23/02/2026</x:v>
+        <x:v>12/02/2026</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>24/02/2026</x:v>
+        <x:v>12/02/2026</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>25/02/2026</x:v>
+        <x:v>13/02/2026</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>150</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R23" t="n">
-        <x:v>150</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T23" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4346,59 +5250,59 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>Yessica Flores</x:v>
+        <x:v>Alejandra Melendez</x:v>
       </x:c>
       <x:c r="C24" t="str"/>
       <x:c r="D24" t="n">
-        <x:v>150</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>YESSICA FLORES CAMBORDA</x:v>
+        <x:v>Alejandra Melendez</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>10263253</x:v>
+        <x:v>45938079</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>51998334629</x:v>
+        <x:v>997037652</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M24" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>25/02/2026</x:v>
+        <x:v>14/02/2026</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>25/02/2026</x:v>
+        <x:v>20/02/2026</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>27/03/2026</x:v>
+        <x:v>22/03/2026</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R24" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T24" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4406,26 +5310,26 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>Gino Peralta</x:v>
+        <x:v>Yessica Flores</x:v>
       </x:c>
       <x:c r="C25" t="str"/>
       <x:c r="D25" t="n">
-        <x:v>779</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>Form meta</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>Gino Peralta</x:v>
+        <x:v>YESSICA FLORES CAMBORDA</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>75896545</x:v>
+        <x:v>10263253</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>998316531</x:v>
+        <x:v>51998334629</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Nuevo</x:v>
@@ -4434,31 +5338,31 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>24/02/2026</x:v>
+        <x:v>23/02/2026</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>24/02/2026</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>14/04/2026</x:v>
+        <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="Q25" t="n">
-        <x:v>779</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="R25" t="n">
-        <x:v>779</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="S25" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T25" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4466,38 +5370,38 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>Ivan Zamora</x:v>
+        <x:v>Yessica Flores</x:v>
       </x:c>
       <x:c r="C26" t="str"/>
       <x:c r="D26" t="n">
-        <x:v>80</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Form web</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>Ivan Zamora</x:v>
+        <x:v>YESSICA FLORES CAMBORDA</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>001109312</x:v>
+        <x:v>10263253</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>961856326</x:v>
+        <x:v>51998334629</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N26" t="str">
         <x:v>25/02/2026</x:v>
@@ -4506,19 +5410,19 @@
         <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>26/02/2026</x:v>
+        <x:v>27/03/2026</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>80</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R26" t="n">
-        <x:v>80</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T26" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4526,29 +5430,29 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>Ivan Zamora</x:v>
+        <x:v>Gino Peralta</x:v>
       </x:c>
       <x:c r="C27" t="str"/>
       <x:c r="D27" t="n">
-        <x:v>80</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>Form web</x:v>
+        <x:v>Form meta</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>Ivan Zamora</x:v>
+        <x:v>Gino Peralta</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>001109312</x:v>
+        <x:v>75896545</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>961856326</x:v>
+        <x:v>998316531</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K27" t="str">
         <x:v>Walk in</x:v>
@@ -4560,19 +5464,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>30/03/2026</x:v>
+        <x:v>24/02/2026</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>01/04/2026</x:v>
+        <x:v>24/02/2026</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>01/05/2026</x:v>
+        <x:v>14/04/2026</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R27" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S27" t="n">
         <x:v>0</x:v>
@@ -4608,37 +5512,37 @@
         <x:v>961856326</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>04/05/2026</x:v>
+        <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>04/05/2026</x:v>
+        <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>03/06/2026</x:v>
+        <x:v>26/02/2026</x:v>
       </x:c>
       <x:c r="Q28" t="n">
-        <x:v>779</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R28" t="n">
-        <x:v>779</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S28" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T28" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4646,11 +5550,11 @@
         <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>Anelle Kaplisvsy</x:v>
+        <x:v>Ivan Zamora</x:v>
       </x:c>
       <x:c r="C29" t="str"/>
       <x:c r="D29" t="n">
-        <x:v>579</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E29" t="str">
         <x:v>Form web</x:v>
@@ -4659,16 +5563,16 @@
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>Anelle Kaplisvsy</x:v>
+        <x:v>Ivan Zamora</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>73451163</x:v>
+        <x:v>001109312</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>997516811</x:v>
+        <x:v>961856326</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K29" t="str">
         <x:v>Walk in</x:v>
@@ -4680,13 +5584,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>25/02/2026</x:v>
+        <x:v>30/03/2026</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>25/02/2026</x:v>
+        <x:v>01/04/2026</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>10/04/2026</x:v>
+        <x:v>01/05/2026</x:v>
       </x:c>
       <x:c r="Q29" t="n">
         <x:v>579</x:v>
@@ -4703,37 +5607,35 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>Marzo 2026</x:v>
+        <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>Alexis Zorrilla</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>989834598</x:v>
-      </x:c>
+        <x:v>Ivan Zamora</x:v>
+      </x:c>
+      <x:c r="C30" t="str"/>
       <x:c r="D30" t="n">
-        <x:v>579</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form web</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>Alexis Zorrilla</x:v>
+        <x:v>Ivan Zamora</x:v>
       </x:c>
       <x:c r="H30" t="str">
-        <x:v>44134863</x:v>
+        <x:v>001109312</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>+51 989 834 598</x:v>
+        <x:v>961856326</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L30" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4742,60 +5644,58 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>12/03/2026</x:v>
+        <x:v>04/05/2026</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>12/03/2026</x:v>
+        <x:v>04/05/2026</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>11/04/2026</x:v>
+        <x:v>03/06/2026</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R30" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T30" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>Marzo 2026</x:v>
+        <x:v>Febrero 2026</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>Alexis Zorrilla</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>989834598</x:v>
-      </x:c>
+        <x:v>Anelle Kaplisvsy</x:v>
+      </x:c>
+      <x:c r="C31" t="str"/>
       <x:c r="D31" t="n">
         <x:v>579</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form web</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>Alexis Zorrilla</x:v>
+        <x:v>Anelle Kaplisvsy</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>44134863</x:v>
+        <x:v>73451163</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>+51 989 834 598</x:v>
+        <x:v>997516811</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L31" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4804,13 +5704,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>01/04/2026</x:v>
+        <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>09/04/2026</x:v>
+        <x:v>25/02/2026</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>09/05/2026</x:v>
+        <x:v>10/04/2026</x:v>
       </x:c>
       <x:c r="Q31" t="n">
         <x:v>579</x:v>
@@ -4822,7 +5722,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T31" t="str">
-        <x:v>erikavta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4854,10 +5754,10 @@
         <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L32" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4866,13 +5766,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>12/03/2026</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>26/05/2026</x:v>
+        <x:v>12/03/2026</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>11/04/2026</x:v>
       </x:c>
       <x:c r="Q32" t="n">
         <x:v>579</x:v>
@@ -4884,7 +5784,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T32" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4892,61 +5792,61 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>969485253</x:v>
+        <x:v>989834598</x:v>
       </x:c>
       <x:c r="D33" t="n">
-        <x:v>859</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F33" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="H33" t="str">
-        <x:v>47356525</x:v>
+        <x:v>44134863</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>969485253</x:v>
+        <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L33" t="str">
         <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M33" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>16/03/2026</x:v>
+        <x:v>01/04/2026</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>16/03/2026</x:v>
+        <x:v>09/04/2026</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>17/03/2026</x:v>
+        <x:v>09/05/2026</x:v>
       </x:c>
       <x:c r="Q33" t="n">
-        <x:v>160</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R33" t="n">
-        <x:v>160</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S33" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T33" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>erikavta</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4954,34 +5854,34 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>969485253</x:v>
+        <x:v>989834598</x:v>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>859</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="H34" t="str">
-        <x:v>47356525</x:v>
+        <x:v>44134863</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>969485253</x:v>
+        <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L34" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -4990,25 +5890,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>26/05/2026</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>21/04/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>779</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R34" t="n">
-        <x:v>779</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S34" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T34" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -5016,55 +5916,55 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>969485253</x:v>
+        <x:v>989834598</x:v>
       </x:c>
       <x:c r="D35" t="n">
-        <x:v>859</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="H35" t="str">
-        <x:v>47356525</x:v>
+        <x:v>44134863</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>969485253</x:v>
+        <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>NUTRICIÓN</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M35" t="str">
-        <x:v>3 meses</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>08/04/2026</x:v>
+        <x:v>07/07/2026</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>08/04/2026</x:v>
+        <x:v>07/07/2026</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>24/05/2026</x:v>
+        <x:v>06/08/2026</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>700</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R35" t="n">
-        <x:v>700</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S35" t="n">
         <x:v>0</x:v>
@@ -5078,34 +5978,34 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>969485253</x:v>
+        <x:v>989834598</x:v>
       </x:c>
       <x:c r="D36" t="n">
-        <x:v>859</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G36" t="str">
-        <x:v>Jimena Oliva Respaldiza</x:v>
+        <x:v>Alexis Zorrilla</x:v>
       </x:c>
       <x:c r="H36" t="str">
-        <x:v>47356525</x:v>
+        <x:v>44134863</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>969485253</x:v>
+        <x:v>+51 989 834 598</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L36" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -5114,25 +6014,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>20/04/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>20/04/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>779</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R36" t="n">
-        <x:v>779</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T36" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -5140,10 +6040,10 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>Vannesa Oliva Respaldiza</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>994222283</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="D37" t="n">
         <x:v>859</x:v>
@@ -5155,40 +6055,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>Vannesa Oliva Respaldiza</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H37" t="str">
-        <x:v>47357945</x:v>
+        <x:v>47356525</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>994222283</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L37" t="str">
         <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>16/03/2026</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>16/03/2026</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>18/04/2026</x:v>
+        <x:v>17/03/2026</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>779</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="R37" t="n">
-        <x:v>779</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="S37" t="n">
         <x:v>0</x:v>
@@ -5202,10 +6102,10 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>Vannesa Oliva Respaldiza</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>994222283</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>859</x:v>
@@ -5217,16 +6117,16 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>Vannesa Oliva Respaldiza</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H38" t="str">
-        <x:v>47357945</x:v>
+        <x:v>47356525</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>994222283</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K38" t="str">
         <x:v>Walk in</x:v>
@@ -5238,13 +6138,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>14/04/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>20/04/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>21/04/2026</x:v>
       </x:c>
       <x:c r="Q38" t="n">
         <x:v>779</x:v>
@@ -5256,7 +6156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T38" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -5264,61 +6164,61 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>Natalia Barreda</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>959206483</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="D39" t="n">
-        <x:v>150</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E39" t="str">
-        <x:v>Form meta</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F39" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>Natalia Barreda Dominguez</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H39" t="str">
-        <x:v>29640537</x:v>
+        <x:v>47356525</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>51959 206 483</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>NUTRICIÓN</x:v>
       </x:c>
       <x:c r="M39" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>3 meses</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>17/03/2026</x:v>
+        <x:v>08/04/2026</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>17/03/2026</x:v>
+        <x:v>08/04/2026</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>18/03/2026</x:v>
+        <x:v>24/05/2026</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>150</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="R39" t="n">
-        <x:v>150</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="S39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T39" t="str">
-        <x:v>erikavta</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -5326,34 +6226,34 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>924699583</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="D40" t="n">
-        <x:v>779</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E40" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F40" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Jimena Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H40" t="str">
-        <x:v>001198860</x:v>
+        <x:v>47356525</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>924699583</x:v>
+        <x:v>969485253</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L40" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -5362,13 +6262,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>20/04/2026</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>19/03/2026</x:v>
+        <x:v>20/04/2026</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>18/04/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="Q40" t="n">
         <x:v>779</x:v>
@@ -5380,7 +6280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T40" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -5388,31 +6288,31 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Vannesa Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>924699583</x:v>
+        <x:v>994222283</x:v>
       </x:c>
       <x:c r="D41" t="n">
-        <x:v>779</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E41" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F41" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Vannesa Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H41" t="str">
-        <x:v>001198860</x:v>
+        <x:v>47357945</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>924699583</x:v>
+        <x:v>994222283</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K41" t="str">
         <x:v>Walk in</x:v>
@@ -5424,25 +6324,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>06/04/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>04/05/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>03/06/2026</x:v>
+        <x:v>18/04/2026</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R41" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S41" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T41" t="str">
-        <x:v>tatianamerel</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -5450,34 +6350,34 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Vannesa Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>924699583</x:v>
+        <x:v>994222283</x:v>
       </x:c>
       <x:c r="D42" t="n">
-        <x:v>779</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E42" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F42" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G42" t="str">
-        <x:v>Karla Lopez</x:v>
+        <x:v>Vannesa Oliva Respaldiza</x:v>
       </x:c>
       <x:c r="H42" t="str">
-        <x:v>001198860</x:v>
+        <x:v>47357945</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>924699583</x:v>
+        <x:v>994222283</x:v>
       </x:c>
       <x:c r="J42" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L42" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -5486,25 +6386,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N42" t="str">
-        <x:v>26/05/2026</x:v>
+        <x:v>14/04/2026</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>26/05/2026</x:v>
+        <x:v>20/04/2026</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="Q42" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R42" t="n">
-        <x:v>579</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T42" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -5512,34 +6412,34 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>Stefanie Kronenberg</x:v>
+        <x:v>Natalia Barreda</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>989246127</x:v>
+        <x:v>959206483</x:v>
       </x:c>
       <x:c r="D43" t="n">
-        <x:v>2219</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E43" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Form meta</x:v>
       </x:c>
       <x:c r="F43" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>Stefanie Kronenberg</x:v>
+        <x:v>Natalia Barreda Dominguez</x:v>
       </x:c>
       <x:c r="H43" t="str">
-        <x:v>06408476</x:v>
+        <x:v>29640537</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>989246127</x:v>
+        <x:v>51959 206 483</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L43" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -5548,13 +6448,13 @@
         <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>23/03/2026</x:v>
+        <x:v>17/03/2026</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>23/03/2026</x:v>
+        <x:v>17/03/2026</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>24/03/2026</x:v>
+        <x:v>18/03/2026</x:v>
       </x:c>
       <x:c r="Q43" t="n">
         <x:v>150</x:v>
@@ -5566,7 +6466,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T43" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>erikavta</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -5574,55 +6474,55 @@
         <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>Stefanie Kronenberg</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>989246127</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="D44" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E44" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F44" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G44" t="str">
-        <x:v>Stefanie Kronenberg</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="H44" t="str">
-        <x:v>06408476</x:v>
+        <x:v>001198860</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>989246127</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M44" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>23/03/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>13/05/2026</x:v>
+        <x:v>19/03/2026</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>12/06/2026</x:v>
+        <x:v>18/04/2026</x:v>
       </x:c>
       <x:c r="Q44" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R44" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S44" t="n">
         <x:v>0</x:v>
@@ -5633,161 +6533,161 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>Jocelyne Jurado</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>966440064</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="D45" t="n">
-        <x:v>1900</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E45" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F45" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G45" t="str">
-        <x:v>Jocelyne Jurado</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="H45" t="str">
-        <x:v>43120256</x:v>
+        <x:v>001198860</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>51966440064</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M45" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>06/04/2026</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>07/04/2026</x:v>
+        <x:v>04/05/2026</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>22/04/2026</x:v>
+        <x:v>03/06/2026</x:v>
       </x:c>
       <x:c r="Q45" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R45" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T45" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>tatianamerel</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>Geraldine Caycho</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="D46" t="n">
-        <x:v>1900</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E46" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F46" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G46" t="str">
-        <x:v>Geraldine Caycho Morales</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="H46" t="str">
-        <x:v>48088486</x:v>
+        <x:v>001198860</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M46" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N46" t="str">
-        <x:v>01/04/2026</x:v>
+        <x:v>26/05/2026</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>07/04/2026</x:v>
+        <x:v>26/05/2026</x:v>
       </x:c>
       <x:c r="P46" t="str">
-        <x:v>22/04/2026</x:v>
+        <x:v>25/06/2026</x:v>
       </x:c>
       <x:c r="Q46" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R46" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S46" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T46" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>Geraldine Caycho</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="D47" t="n">
-        <x:v>1900</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E47" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F47" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G47" t="str">
-        <x:v>Geraldine Caycho Morales</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="H47" t="str">
-        <x:v>48088486</x:v>
+        <x:v>001198860</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L47" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -5796,19 +6696,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N47" t="str">
-        <x:v>15/04/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>21/04/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="P47" t="str">
-        <x:v>26/05/2026</x:v>
+        <x:v>16/08/2026</x:v>
       </x:c>
       <x:c r="Q47" t="n">
-        <x:v>1169</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R47" t="n">
-        <x:v>1169</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S47" t="n">
         <x:v>0</x:v>
@@ -5819,37 +6719,37 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>Geraldine Caycho</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="D48" t="n">
-        <x:v>1900</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E48" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F48" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G48" t="str">
-        <x:v>Geraldine Caycho Morales</x:v>
+        <x:v>Karla Lopez</x:v>
       </x:c>
       <x:c r="H48" t="str">
-        <x:v>48088486</x:v>
+        <x:v>001198860</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>939267977</x:v>
+        <x:v>924699583</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L48" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -5858,19 +6758,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N48" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>09/06/2026</x:v>
+        <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="P48" t="str">
-        <x:v>09/07/2026</x:v>
+        <x:v>17/09/2026</x:v>
       </x:c>
       <x:c r="Q48" t="n">
-        <x:v>1169</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R48" t="n">
-        <x:v>1169</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S48" t="n">
         <x:v>0</x:v>
@@ -5881,120 +6781,120 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>Geraldine Caycho</x:v>
+        <x:v>Stefanie Kronenberg</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>939267977</x:v>
+        <x:v>989246127</x:v>
       </x:c>
       <x:c r="D49" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E49" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F49" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G49" t="str">
-        <x:v>Geraldine Caycho Morales</x:v>
+        <x:v>Stefanie Kronenberg</x:v>
       </x:c>
       <x:c r="H49" t="str">
-        <x:v>48088486</x:v>
+        <x:v>06408476</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>939267977</x:v>
+        <x:v>989246127</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M49" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N49" t="str">
-        <x:v>29/06/2026</x:v>
+        <x:v>23/03/2026</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>23/03/2026</x:v>
       </x:c>
       <x:c r="P49" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>24/03/2026</x:v>
       </x:c>
       <x:c r="Q49" t="n">
-        <x:v>1169</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="R49" t="n">
-        <x:v>1169</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="S49" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T49" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>Abril 2026</x:v>
+        <x:v>Marzo 2026</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Stefanie Kronenberg</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>985773253</x:v>
+        <x:v>989246127</x:v>
       </x:c>
       <x:c r="D50" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E50" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F50" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G50" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Stefanie Kronenberg</x:v>
       </x:c>
       <x:c r="H50" t="str">
-        <x:v>45589084</x:v>
+        <x:v>06408476</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>985773253</x:v>
+        <x:v>989246127</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L50" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M50" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N50" t="str">
-        <x:v>06/04/2026</x:v>
+        <x:v>23/03/2026</x:v>
       </x:c>
       <x:c r="O50" t="str">
-        <x:v>07/04/2026</x:v>
+        <x:v>13/05/2026</x:v>
       </x:c>
       <x:c r="P50" t="str">
-        <x:v>22/04/2026</x:v>
+        <x:v>12/06/2026</x:v>
       </x:c>
       <x:c r="Q50" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R50" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S50" t="n">
         <x:v>0</x:v>
@@ -6008,10 +6908,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Jocelyne Jurado</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>985773253</x:v>
+        <x:v>966440064</x:v>
       </x:c>
       <x:c r="D51" t="n">
         <x:v>1900</x:v>
@@ -6023,46 +6923,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G51" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Jocelyne Jurado</x:v>
       </x:c>
       <x:c r="H51" t="str">
-        <x:v>45589084</x:v>
+        <x:v>43120256</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>985773253</x:v>
+        <x:v>51966440064</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L51" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M51" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N51" t="str">
-        <x:v>16/04/2026</x:v>
+        <x:v>06/04/2026</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>16/04/2026</x:v>
+        <x:v>07/04/2026</x:v>
       </x:c>
       <x:c r="P51" t="str">
-        <x:v>16/05/2026</x:v>
+        <x:v>22/04/2026</x:v>
       </x:c>
       <x:c r="Q51" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R51" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S51" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T51" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -6070,10 +6970,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="D52" t="n">
         <x:v>1900</x:v>
@@ -6085,46 +6985,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G52" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho Morales</x:v>
       </x:c>
       <x:c r="H52" t="str">
-        <x:v>45589084</x:v>
+        <x:v>48088486</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L52" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M52" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N52" t="str">
-        <x:v>14/05/2026</x:v>
+        <x:v>01/04/2026</x:v>
       </x:c>
       <x:c r="O52" t="str">
-        <x:v>14/05/2026</x:v>
+        <x:v>07/04/2026</x:v>
       </x:c>
       <x:c r="P52" t="str">
-        <x:v>13/06/2026</x:v>
+        <x:v>22/04/2026</x:v>
       </x:c>
       <x:c r="Q52" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R52" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T52" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -6132,10 +7032,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="D53" t="n">
         <x:v>1900</x:v>
@@ -6147,40 +7047,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G53" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho Morales</x:v>
       </x:c>
       <x:c r="H53" t="str">
-        <x:v>45589084</x:v>
+        <x:v>48088486</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M53" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N53" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>15/04/2026</x:v>
       </x:c>
       <x:c r="O53" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>21/04/2026</x:v>
       </x:c>
       <x:c r="P53" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>26/05/2026</x:v>
       </x:c>
       <x:c r="Q53" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R53" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S53" t="n">
         <x:v>0</x:v>
@@ -6194,10 +7094,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="D54" t="n">
         <x:v>1900</x:v>
@@ -6209,13 +7109,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G54" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho Morales</x:v>
       </x:c>
       <x:c r="H54" t="str">
-        <x:v>45589084</x:v>
+        <x:v>48088486</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Renovacion</x:v>
@@ -6224,25 +7124,25 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M54" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N54" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>16/06/2026</x:v>
+        <x:v>09/06/2026</x:v>
       </x:c>
       <x:c r="P54" t="str">
-        <x:v>16/07/2026</x:v>
+        <x:v>09/07/2026</x:v>
       </x:c>
       <x:c r="Q54" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R54" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S54" t="n">
         <x:v>0</x:v>
@@ -6256,10 +7156,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="D55" t="n">
         <x:v>1900</x:v>
@@ -6271,13 +7171,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G55" t="str">
-        <x:v>Silvia Canales</x:v>
+        <x:v>Geraldine Caycho Morales</x:v>
       </x:c>
       <x:c r="H55" t="str">
-        <x:v>45589084</x:v>
+        <x:v>48088486</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>985773253</x:v>
+        <x:v>939267977</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Renovacion</x:v>
@@ -6286,25 +7186,25 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M55" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N55" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>29/06/2026</x:v>
       </x:c>
       <x:c r="O55" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="P55" t="str">
-        <x:v>09/08/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="Q55" t="n">
-        <x:v>3029</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R55" t="n">
-        <x:v>3029</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S55" t="n">
         <x:v>0</x:v>
@@ -6318,55 +7218,55 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D56" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E56" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F56" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G56" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H56" t="str">
-        <x:v>10134937</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>51922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L56" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M56" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N56" t="str">
+        <x:v>06/04/2026</x:v>
+      </x:c>
+      <x:c r="O56" t="str">
         <x:v>07/04/2026</x:v>
       </x:c>
-      <x:c r="O56" t="str">
-        <x:v>16/04/2026</x:v>
-      </x:c>
       <x:c r="P56" t="str">
-        <x:v>16/05/2026</x:v>
+        <x:v>22/04/2026</x:v>
       </x:c>
       <x:c r="Q56" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R56" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S56" t="n">
         <x:v>0</x:v>
@@ -6380,28 +7280,28 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D57" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E57" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F57" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G57" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H57" t="str">
-        <x:v>10134937</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>51922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Renovacion</x:v>
@@ -6416,13 +7316,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N57" t="str">
-        <x:v>20/05/2026</x:v>
+        <x:v>16/04/2026</x:v>
       </x:c>
       <x:c r="O57" t="str">
-        <x:v>20/05/2026</x:v>
+        <x:v>16/04/2026</x:v>
       </x:c>
       <x:c r="P57" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>16/05/2026</x:v>
       </x:c>
       <x:c r="Q57" t="n">
         <x:v>2219</x:v>
@@ -6442,28 +7342,28 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D58" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E58" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F58" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G58" t="str">
-        <x:v>Walter de la Torre</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H58" t="str">
-        <x:v>10134937</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>51922218809</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Renovacion</x:v>
@@ -6478,19 +7378,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N58" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>14/05/2026</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>14/05/2026</x:v>
       </x:c>
       <x:c r="P58" t="str">
-        <x:v>19/07/2026</x:v>
+        <x:v>13/06/2026</x:v>
       </x:c>
       <x:c r="Q58" t="n">
-        <x:v>2214</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R58" t="n">
-        <x:v>2214</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S58" t="n">
         <x:v>0</x:v>
@@ -6504,10 +7404,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D59" t="n">
         <x:v>1900</x:v>
@@ -6519,46 +7419,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G59" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H59" t="str">
-        <x:v>73035854</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L59" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M59" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N59" t="str">
-        <x:v>14/04/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="O59" t="str">
-        <x:v>14/04/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="P59" t="str">
-        <x:v>29/04/2026</x:v>
+        <x:v>11/07/2026</x:v>
       </x:c>
       <x:c r="Q59" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R59" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S59" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T59" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -6566,10 +7466,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D60" t="n">
         <x:v>1900</x:v>
@@ -6581,46 +7481,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G60" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H60" t="str">
-        <x:v>73035854</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L60" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M60" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N60" t="str">
-        <x:v>24/04/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="O60" t="str">
-        <x:v>24/04/2026</x:v>
+        <x:v>16/06/2026</x:v>
       </x:c>
       <x:c r="P60" t="str">
-        <x:v>24/05/2026</x:v>
+        <x:v>16/07/2026</x:v>
       </x:c>
       <x:c r="Q60" t="n">
-        <x:v>779</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R60" t="n">
-        <x:v>779</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S60" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T60" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -6628,10 +7528,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D61" t="n">
         <x:v>1900</x:v>
@@ -6643,13 +7543,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G61" t="str">
-        <x:v>Julian Cuadros</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H61" t="str">
-        <x:v>73035854</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>980636903</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>Renovacion</x:v>
@@ -6658,31 +7558,31 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L61" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M61" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N61" t="str">
-        <x:v>28/05/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O61" t="str">
-        <x:v>28/05/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P61" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q61" t="n">
-        <x:v>779</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R61" t="n">
-        <x:v>779</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S61" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T61" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -6690,61 +7590,61 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>Oscar Dufour</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>987813637</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="D62" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F62" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G62" t="str">
-        <x:v>Oscar Dufour</x:v>
+        <x:v>Silvia Canales</x:v>
       </x:c>
       <x:c r="H62" t="str">
-        <x:v>09394682</x:v>
+        <x:v>45589084</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>987813637</x:v>
+        <x:v>985773253</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L62" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M62" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N62" t="str">
-        <x:v>14/04/2026</x:v>
+        <x:v>11/08/2026</x:v>
       </x:c>
       <x:c r="O62" t="str">
-        <x:v>01/06/2026</x:v>
+        <x:v>11/08/2026</x:v>
       </x:c>
       <x:c r="P62" t="str">
-        <x:v>16/06/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="Q62" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R62" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S62" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T62" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -6752,13 +7652,13 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>Mariana Viloria</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>997755931</x:v>
+        <x:v>922218809</x:v>
       </x:c>
       <x:c r="D63" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E63" t="str">
         <x:v>Form Meta</x:v>
@@ -6767,40 +7667,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G63" t="str">
-        <x:v>Mariana Viloria</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="H63" t="str">
-        <x:v>000244077</x:v>
+        <x:v>10134937</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>997755931</x:v>
+        <x:v>51922218809</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L63" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M63" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N63" t="str">
-        <x:v>22/04/2026</x:v>
+        <x:v>07/04/2026</x:v>
       </x:c>
       <x:c r="O63" t="str">
-        <x:v>28/04/2026</x:v>
+        <x:v>16/04/2026</x:v>
       </x:c>
       <x:c r="P63" t="str">
-        <x:v>13/05/2026</x:v>
+        <x:v>16/05/2026</x:v>
       </x:c>
       <x:c r="Q63" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R63" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S63" t="n">
         <x:v>0</x:v>
@@ -6814,13 +7714,13 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>Mariana Viloria</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>997755931</x:v>
+        <x:v>922218809</x:v>
       </x:c>
       <x:c r="D64" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E64" t="str">
         <x:v>Form Meta</x:v>
@@ -6829,13 +7729,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G64" t="str">
-        <x:v>Mariana Viloria</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="H64" t="str">
-        <x:v>000244077</x:v>
+        <x:v>10134937</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>997755931</x:v>
+        <x:v>51922218809</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>Renovacion</x:v>
@@ -6844,25 +7744,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L64" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M64" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N64" t="str">
-        <x:v>13/05/2026</x:v>
+        <x:v>20/05/2026</x:v>
       </x:c>
       <x:c r="O64" t="str">
-        <x:v>13/05/2026</x:v>
+        <x:v>20/05/2026</x:v>
       </x:c>
       <x:c r="P64" t="str">
-        <x:v>12/06/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="Q64" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R64" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S64" t="n">
         <x:v>0</x:v>
@@ -6876,61 +7776,61 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>Romina Chirinos</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>962771928</x:v>
+        <x:v>922218809</x:v>
       </x:c>
       <x:c r="D65" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E65" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F65" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G65" t="str">
-        <x:v>Romina Chirinos</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="H65" t="str">
-        <x:v>44079192</x:v>
+        <x:v>10134937</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>962771928</x:v>
+        <x:v>51922218809</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L65" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M65" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N65" t="str">
-        <x:v>24/04/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="O65" t="str">
-        <x:v>24/04/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="P65" t="str">
-        <x:v>09/05/2026</x:v>
+        <x:v>19/07/2026</x:v>
       </x:c>
       <x:c r="Q65" t="n">
-        <x:v>1000</x:v>
+        <x:v>2214</x:v>
       </x:c>
       <x:c r="R65" t="n">
-        <x:v>1000</x:v>
+        <x:v>2214</x:v>
       </x:c>
       <x:c r="S65" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T65" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -6938,28 +7838,28 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>Romina Chirinos</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>962771928</x:v>
+        <x:v>922218809</x:v>
       </x:c>
       <x:c r="D66" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E66" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F66" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G66" t="str">
-        <x:v>Romina Chirinos</x:v>
+        <x:v>Walter de la Torre</x:v>
       </x:c>
       <x:c r="H66" t="str">
-        <x:v>44079192</x:v>
+        <x:v>10134937</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>962771928</x:v>
+        <x:v>51922218809</x:v>
       </x:c>
       <x:c r="J66" t="str">
         <x:v>Renovacion</x:v>
@@ -6968,31 +7868,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L66" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M66" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N66" t="str">
-        <x:v>07/05/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O66" t="str">
-        <x:v>20/05/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P66" t="str">
-        <x:v>20/06/2026</x:v>
+        <x:v>22/08/2026</x:v>
       </x:c>
       <x:c r="Q66" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R66" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S66" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T66" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -7000,10 +7900,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="D67" t="n">
         <x:v>1900</x:v>
@@ -7015,19 +7915,19 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G67" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="H67" t="str">
-        <x:v>40783552</x:v>
+        <x:v>73035854</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="J67" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L67" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -7036,13 +7936,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N67" t="str">
-        <x:v>27/04/2026</x:v>
+        <x:v>14/04/2026</x:v>
       </x:c>
       <x:c r="O67" t="str">
-        <x:v>27/04/2026</x:v>
+        <x:v>14/04/2026</x:v>
       </x:c>
       <x:c r="P67" t="str">
-        <x:v>10/05/2026</x:v>
+        <x:v>29/04/2026</x:v>
       </x:c>
       <x:c r="Q67" t="n">
         <x:v>1000</x:v>
@@ -7062,10 +7962,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="D68" t="n">
         <x:v>1900</x:v>
@@ -7077,13 +7977,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G68" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="H68" t="str">
-        <x:v>40783552</x:v>
+        <x:v>73035854</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="J68" t="str">
         <x:v>Renovacion</x:v>
@@ -7092,25 +7992,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M68" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N68" t="str">
-        <x:v>19/05/2026</x:v>
+        <x:v>24/04/2026</x:v>
       </x:c>
       <x:c r="O68" t="str">
-        <x:v>19/05/2026</x:v>
+        <x:v>24/04/2026</x:v>
       </x:c>
       <x:c r="P68" t="str">
-        <x:v>18/06/2026</x:v>
+        <x:v>24/05/2026</x:v>
       </x:c>
       <x:c r="Q68" t="n">
-        <x:v>3029</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R68" t="n">
-        <x:v>3029</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S68" t="n">
         <x:v>0</x:v>
@@ -7124,10 +8024,10 @@
         <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="D69" t="n">
         <x:v>1900</x:v>
@@ -7139,19 +8039,19 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G69" t="str">
-        <x:v>Luis Rodriguez</x:v>
+        <x:v>Julian Cuadros</x:v>
       </x:c>
       <x:c r="H69" t="str">
-        <x:v>40783552</x:v>
+        <x:v>73035854</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>959237010</x:v>
+        <x:v>980636903</x:v>
       </x:c>
       <x:c r="J69" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L69" t="str">
         <x:v>MEMBRESÍA</x:v>
@@ -7160,81 +8060,81 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N69" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>28/05/2026</x:v>
       </x:c>
       <x:c r="O69" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>28/05/2026</x:v>
       </x:c>
       <x:c r="P69" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="Q69" t="n">
-        <x:v>1169</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R69" t="n">
-        <x:v>1169</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S69" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T69" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>Mathias Brivio</x:v>
+        <x:v>Oscar Dufour</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>999197080</x:v>
+        <x:v>987813637</x:v>
       </x:c>
       <x:c r="D70" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E70" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F70" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G70" t="str">
-        <x:v>Mathias Brivio</x:v>
+        <x:v>Oscar Dufour</x:v>
       </x:c>
       <x:c r="H70" t="str">
-        <x:v>10268598</x:v>
+        <x:v>09394682</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>999197080</x:v>
+        <x:v>987813637</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L70" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M70" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N70" t="str">
-        <x:v>12/05/2026</x:v>
+        <x:v>14/04/2026</x:v>
       </x:c>
       <x:c r="O70" t="str">
-        <x:v>12/05/2026</x:v>
+        <x:v>01/06/2026</x:v>
       </x:c>
       <x:c r="P70" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>16/06/2026</x:v>
       </x:c>
       <x:c r="Q70" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R70" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S70" t="n">
         <x:v>0</x:v>
@@ -7245,16 +8145,16 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mariana Viloria</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>986645733</x:v>
+        <x:v>997755931</x:v>
       </x:c>
       <x:c r="D71" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E71" t="str">
         <x:v>Form Meta</x:v>
@@ -7263,13 +8163,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mariana Viloria</x:v>
       </x:c>
       <x:c r="H71" t="str">
-        <x:v>08217010</x:v>
+        <x:v>000244077</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>986645733</x:v>
+        <x:v>997755931</x:v>
       </x:c>
       <x:c r="J71" t="str">
         <x:v>Nuevo</x:v>
@@ -7281,22 +8181,22 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M71" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N71" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>22/04/2026</x:v>
       </x:c>
       <x:c r="O71" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>28/04/2026</x:v>
       </x:c>
       <x:c r="P71" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>13/05/2026</x:v>
       </x:c>
       <x:c r="Q71" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R71" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S71" t="n">
         <x:v>0</x:v>
@@ -7307,16 +8207,16 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mariana Viloria</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>986645733</x:v>
+        <x:v>997755931</x:v>
       </x:c>
       <x:c r="D72" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E72" t="str">
         <x:v>Form Meta</x:v>
@@ -7325,40 +8225,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G72" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mariana Viloria</x:v>
       </x:c>
       <x:c r="H72" t="str">
-        <x:v>08217010</x:v>
+        <x:v>000244077</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>986645733</x:v>
+        <x:v>997755931</x:v>
       </x:c>
       <x:c r="J72" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M72" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N72" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>13/05/2026</x:v>
       </x:c>
       <x:c r="O72" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>13/05/2026</x:v>
       </x:c>
       <x:c r="P72" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/06/2026</x:v>
       </x:c>
       <x:c r="Q72" t="n">
-        <x:v>2219</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R72" t="n">
-        <x:v>2219</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S72" t="n">
         <x:v>0</x:v>
@@ -7369,31 +8269,31 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>Javier Bracco Puch</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>945678019</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="D73" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E73" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F73" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G73" t="str">
-        <x:v>Javier Edgardo Bracco Puch</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="H73" t="str">
-        <x:v>43226753</x:v>
+        <x:v>44079192</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>51945678019</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Nuevo</x:v>
@@ -7408,13 +8308,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N73" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>24/04/2026</x:v>
       </x:c>
       <x:c r="O73" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>24/04/2026</x:v>
       </x:c>
       <x:c r="P73" t="str">
-        <x:v>02/06/2026</x:v>
+        <x:v>09/05/2026</x:v>
       </x:c>
       <x:c r="Q73" t="n">
         <x:v>1000</x:v>
@@ -7431,31 +8331,31 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>Javier Bracco Puch</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>945678019</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="D74" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E74" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F74" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G74" t="str">
-        <x:v>Javier Edgardo Bracco Puch</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="H74" t="str">
-        <x:v>43226753</x:v>
+        <x:v>44079192</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>51945678019</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="J74" t="str">
         <x:v>Renovacion</x:v>
@@ -7470,19 +8370,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N74" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>07/05/2026</x:v>
       </x:c>
       <x:c r="O74" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>20/05/2026</x:v>
       </x:c>
       <x:c r="P74" t="str">
-        <x:v>04/07/2026</x:v>
+        <x:v>20/06/2026</x:v>
       </x:c>
       <x:c r="Q74" t="n">
-        <x:v>1169</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R74" t="n">
-        <x:v>1169</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S74" t="n">
         <x:v>0</x:v>
@@ -7493,217 +8393,217 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>998119233</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="D75" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E75" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F75" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G75" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Romina Chirinos</x:v>
       </x:c>
       <x:c r="H75" t="str">
-        <x:v>09399588</x:v>
+        <x:v>44079192</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>998119233</x:v>
+        <x:v>962771928</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L75" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M75" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N75" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="O75" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="P75" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>04/09/2026</x:v>
       </x:c>
       <x:c r="Q75" t="n">
-        <x:v>2219</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R75" t="n">
-        <x:v>2219</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S75" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T75" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>998119233</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="D76" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E76" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F76" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G76" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="H76" t="str">
-        <x:v>09399588</x:v>
+        <x:v>40783552</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>998119233</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L76" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M76" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N76" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>27/04/2026</x:v>
       </x:c>
       <x:c r="O76" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>27/04/2026</x:v>
       </x:c>
       <x:c r="P76" t="str">
-        <x:v>26/07/2026</x:v>
+        <x:v>10/05/2026</x:v>
       </x:c>
       <x:c r="Q76" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R76" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S76" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T76" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>997511543</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="D77" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E77" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F77" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="H77" t="str">
-        <x:v>10223240</x:v>
+        <x:v>40783552</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>51997511543</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L77" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M77" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N77" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>19/05/2026</x:v>
       </x:c>
       <x:c r="O77" t="str">
-        <x:v>02/06/2026</x:v>
+        <x:v>19/05/2026</x:v>
       </x:c>
       <x:c r="P77" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>18/06/2026</x:v>
       </x:c>
       <x:c r="Q77" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R77" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T77" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="C78" t="str">
-        <x:v>997511543</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="D78" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E78" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F78" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G78" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="H78" t="str">
-        <x:v>10223240</x:v>
+        <x:v>40783552</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>51997511543</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="J78" t="str">
         <x:v>Renovacion</x:v>
@@ -7712,25 +8612,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L78" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M78" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N78" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O78" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="P78" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="Q78" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R78" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S78" t="n">
         <x:v>0</x:v>
@@ -7744,28 +8644,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Mathias Brivio</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>951329266</x:v>
+        <x:v>999197080</x:v>
       </x:c>
       <x:c r="D79" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E79" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F79" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Mathias Brivio</x:v>
       </x:c>
       <x:c r="H79" t="str">
-        <x:v>10474396</x:v>
+        <x:v>10268598</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>51951329266</x:v>
+        <x:v>999197080</x:v>
       </x:c>
       <x:c r="J79" t="str">
         <x:v>Nuevo</x:v>
@@ -7777,22 +8677,22 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M79" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N79" t="str">
-        <x:v>29/05/2026</x:v>
+        <x:v>12/05/2026</x:v>
       </x:c>
       <x:c r="O79" t="str">
-        <x:v>29/05/2026</x:v>
+        <x:v>12/05/2026</x:v>
       </x:c>
       <x:c r="P79" t="str">
-        <x:v>16/07/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="Q79" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R79" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S79" t="n">
         <x:v>0</x:v>
@@ -7803,58 +8703,58 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>955098767</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="D80" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E80" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F80" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G80" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="H80" t="str">
-        <x:v>07816623</x:v>
+        <x:v>08217010</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>955098767</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L80" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M80" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N80" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O80" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="P80" t="str">
-        <x:v>23/06/2026</x:v>
+        <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="Q80" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R80" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S80" t="n">
         <x:v>0</x:v>
@@ -7865,34 +8765,34 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>942126985</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="D81" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E81" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F81" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G81" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="H81" t="str">
-        <x:v>07816622</x:v>
+        <x:v>08217010</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>51942126985</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K81" t="str">
         <x:v>Walk in</x:v>
@@ -7901,63 +8801,63 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M81" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N81" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O81" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="P81" t="str">
-        <x:v>23/06/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="Q81" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R81" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S81" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T81" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Javier Bracco Puch</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>983343707</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="D82" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E82" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F82" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G82" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Javier Edgardo Bracco Puch</x:v>
       </x:c>
       <x:c r="H82" t="str">
-        <x:v>42265772</x:v>
+        <x:v>43226753</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>983343707</x:v>
+        <x:v>51945678019</x:v>
       </x:c>
       <x:c r="J82" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L82" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -7966,13 +8866,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N82" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O82" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="P82" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>02/06/2026</x:v>
       </x:c>
       <x:c r="Q82" t="n">
         <x:v>1000</x:v>
@@ -7989,385 +8889,385 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Javier Bracco Puch</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>983343707</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="D83" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F83" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G83" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Javier Edgardo Bracco Puch</x:v>
       </x:c>
       <x:c r="H83" t="str">
-        <x:v>42265772</x:v>
+        <x:v>43226753</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>983343707</x:v>
+        <x:v>51945678019</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N83" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="O83" t="str">
-        <x:v>18/06/2026</x:v>
+        <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="P83" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>04/07/2026</x:v>
       </x:c>
       <x:c r="Q83" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R83" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S83" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T83" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Javier Bracco Puch</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>945127771</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="D84" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E84" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F84" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G84" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Javier Edgardo Bracco Puch</x:v>
       </x:c>
       <x:c r="H84" t="str">
-        <x:v>41687688</x:v>
+        <x:v>43226753</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>51945127771</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L84" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M84" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N84" t="str">
-        <x:v>16/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="O84" t="str">
-        <x:v>18/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P84" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q84" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R84" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S84" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T84" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>945127771</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="D85" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E85" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F85" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="H85" t="str">
-        <x:v>41687688</x:v>
+        <x:v>09399588</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>51945127771</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M85" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N85" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O85" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="P85" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="Q85" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R85" t="n">
-        <x:v>989</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S85" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T85" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>955929014</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="D86" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E86" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F86" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G86" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="H86" t="str">
-        <x:v>42816308</x:v>
+        <x:v>09399588</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>51955929014</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L86" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M86" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N86" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="O86" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="P86" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>26/07/2026</x:v>
       </x:c>
       <x:c r="Q86" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R86" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S86" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T86" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>997921230</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="D87" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E87" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F87" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G87" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="H87" t="str">
-        <x:v>08275871</x:v>
+        <x:v>09399588</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>51997921230</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L87" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M87" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N87" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="O87" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="P87" t="str">
-        <x:v>04/07/2026</x:v>
+        <x:v>03/09/2026</x:v>
       </x:c>
       <x:c r="Q87" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R87" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S87" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T87" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>997921230</x:v>
+        <x:v>997511543</x:v>
       </x:c>
       <x:c r="D88" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E88" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F88" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G88" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="H88" t="str">
-        <x:v>08275871</x:v>
+        <x:v>10223240</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>51997921230</x:v>
+        <x:v>51997511543</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L88" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M88" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N88" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O88" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>02/06/2026</x:v>
       </x:c>
       <x:c r="P88" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="Q88" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R88" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S88" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T88" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>997511543</x:v>
       </x:c>
       <x:c r="D89" t="n">
         <x:v>1900</x:v>
@@ -8379,57 +9279,57 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G89" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="H89" t="str">
-        <x:v>7770642o</x:v>
+        <x:v>10223240</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>51997511543</x:v>
       </x:c>
       <x:c r="J89" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L89" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M89" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N89" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="O89" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="P89" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>11/07/2026</x:v>
       </x:c>
       <x:c r="Q89" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R89" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S89" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T89" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>969714361</x:v>
+        <x:v>951329266</x:v>
       </x:c>
       <x:c r="D90" t="n">
         <x:v>1900</x:v>
@@ -8441,13 +9341,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="H90" t="str">
-        <x:v>71454737</x:v>
+        <x:v>10474396</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>51969714361</x:v>
+        <x:v>51951329266</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>Nuevo</x:v>
@@ -8462,13 +9362,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N90" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>29/05/2026</x:v>
       </x:c>
       <x:c r="O90" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>29/05/2026</x:v>
       </x:c>
       <x:c r="P90" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>16/07/2026</x:v>
       </x:c>
       <x:c r="Q90" t="n">
         <x:v>1000</x:v>
@@ -8485,37 +9385,37 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>951329266</x:v>
       </x:c>
       <x:c r="D91" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F91" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G91" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="H91" t="str">
-        <x:v>10439108</x:v>
+        <x:v>10474396</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>51951329266</x:v>
       </x:c>
       <x:c r="J91" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L91" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -8524,13 +9424,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N91" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="O91" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="P91" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="Q91" t="n">
         <x:v>2219</x:v>
@@ -8542,7 +9442,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T91" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -8550,34 +9450,34 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>Mayte Carolina Pachas Paulino</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="D92" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E92" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F92" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G92" t="str">
-        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="H92" t="str">
-        <x:v>47665207</x:v>
+        <x:v>07816623</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L92" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -8586,13 +9486,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N92" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="O92" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>08/06/2026</x:v>
       </x:c>
       <x:c r="P92" t="str">
-        <x:v>12/07/2026</x:v>
+        <x:v>23/06/2026</x:v>
       </x:c>
       <x:c r="Q92" t="n">
         <x:v>1000</x:v>
@@ -8604,7 +9504,2971 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T92" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>Hernan Bello</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>955098767</x:v>
+      </x:c>
+      <x:c r="D93" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F93" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G93" t="str">
+        <x:v>Hernan Bello</x:v>
+      </x:c>
+      <x:c r="H93" t="str">
+        <x:v>07816623</x:v>
+      </x:c>
+      <x:c r="I93" t="str">
+        <x:v>955098767</x:v>
+      </x:c>
+      <x:c r="J93" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K93" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L93" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N93" t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c r="O93" t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c r="P93" t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c r="Q93" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R93" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T93" t="str">
         <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>Martha Velez</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>942126985</x:v>
+      </x:c>
+      <x:c r="D94" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G94" t="str">
+        <x:v>Martha Velez</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>07816622</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>51942126985</x:v>
+      </x:c>
+      <x:c r="J94" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L94" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N94" t="str">
+        <x:v>04/06/2026</x:v>
+      </x:c>
+      <x:c r="O94" t="str">
+        <x:v>08/06/2026</x:v>
+      </x:c>
+      <x:c r="P94" t="str">
+        <x:v>23/06/2026</x:v>
+      </x:c>
+      <x:c r="Q94" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R94" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T94" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>Martha Velez</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>942126985</x:v>
+      </x:c>
+      <x:c r="D95" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G95" t="str">
+        <x:v>Martha Velez</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>07816622</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>942126985</x:v>
+      </x:c>
+      <x:c r="J95" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L95" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M95" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N95" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="O95" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="P95" t="str">
+        <x:v>23/08/2026</x:v>
+      </x:c>
+      <x:c r="Q95" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R95" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T95" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>Renzo Sotomayor Diaz</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>983343707</x:v>
+      </x:c>
+      <x:c r="D96" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>Instagram</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G96" t="str">
+        <x:v>Renzo Sotomayor Diaz</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>42265772</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>983343707</x:v>
+      </x:c>
+      <x:c r="J96" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L96" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M96" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N96" t="str">
+        <x:v>08/06/2026</x:v>
+      </x:c>
+      <x:c r="O96" t="str">
+        <x:v>11/06/2026</x:v>
+      </x:c>
+      <x:c r="P96" t="str">
+        <x:v>26/06/2026</x:v>
+      </x:c>
+      <x:c r="Q96" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R96" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S96" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T96" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>Renzo Sotomayor Diaz</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>983343707</x:v>
+      </x:c>
+      <x:c r="D97" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>Instagram</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>Renzo Sotomayor Diaz</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>42265772</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>983343707</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M97" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N97" t="str">
+        <x:v>08/06/2026</x:v>
+      </x:c>
+      <x:c r="O97" t="str">
+        <x:v>18/06/2026</x:v>
+      </x:c>
+      <x:c r="P97" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="Q97" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R97" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T97" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>945127771</x:v>
+      </x:c>
+      <x:c r="D98" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>41687688</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>51945127771</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L98" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M98" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N98" t="str">
+        <x:v>16/06/2026</x:v>
+      </x:c>
+      <x:c r="O98" t="str">
+        <x:v>18/06/2026</x:v>
+      </x:c>
+      <x:c r="P98" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="Q98" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R98" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T98" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>945127771</x:v>
+      </x:c>
+      <x:c r="D99" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>41687688</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>51945127771</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L99" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M99" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N99" t="str">
+        <x:v>30/06/2026</x:v>
+      </x:c>
+      <x:c r="O99" t="str">
+        <x:v>30/06/2026</x:v>
+      </x:c>
+      <x:c r="P99" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="Q99" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="R99" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="S99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T99" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>945127771</x:v>
+      </x:c>
+      <x:c r="D100" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>41687688</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>51945127771</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K100" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L100" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M100" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N100" t="str">
+        <x:v>17/07/2026</x:v>
+      </x:c>
+      <x:c r="O100" t="str">
+        <x:v>17/07/2026</x:v>
+      </x:c>
+      <x:c r="P100" t="str">
+        <x:v>16/08/2026</x:v>
+      </x:c>
+      <x:c r="Q100" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="R100" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="S100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T100" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>945127771</x:v>
+      </x:c>
+      <x:c r="D101" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>Andres San Miguel</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>41687688</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>51945127771</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L101" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M101" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N101" t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c r="O101" t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c r="P101" t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c r="Q101" t="n">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="R101" t="n">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="S101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T101" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>Manuel Montes de Oca</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>955929014</x:v>
+      </x:c>
+      <x:c r="D102" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>Manuel Montes de Oca</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>42816308</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>51955929014</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L102" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M102" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N102" t="str">
+        <x:v>17/06/2026</x:v>
+      </x:c>
+      <x:c r="O102" t="str">
+        <x:v>02/07/2026</x:v>
+      </x:c>
+      <x:c r="P102" t="str">
+        <x:v>17/07/2026</x:v>
+      </x:c>
+      <x:c r="Q102" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R102" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T102" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>Manuel Montes de Oca</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>955929014</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>Manuel Montes de Oca</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>42816308</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>51955929014</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>10/07/2026</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>10/07/2026</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>09/08/2026</x:v>
+      </x:c>
+      <x:c r="Q103" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="R103" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="S103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>Beto Mendez</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>997921230</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>Beto Mendez</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>08275871</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>51997921230</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>19/06/2026</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>19/06/2026</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>04/07/2026</x:v>
+      </x:c>
+      <x:c r="Q104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Beto Mendez</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>997921230</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>Beto Mendez</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>08275871</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>51997921230</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>30/06/2026</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>30/06/2026</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="Q105" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="R105" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="S105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Nadia Gutierrez</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>51987504234</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>Nadia Gutierrez</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>7770642o</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>51987504234</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>25/06/2026</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>25/06/2026</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>10/07/2026</x:v>
+      </x:c>
+      <x:c r="Q106" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R106" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>Nadia Gutierrez</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>51987504234</x:v>
+      </x:c>
+      <x:c r="D107" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>Nadia Gutierrez</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>7770642o</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>987504234</x:v>
+      </x:c>
+      <x:c r="J107" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L107" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M107" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N107" t="str">
+        <x:v>20/07/2026</x:v>
+      </x:c>
+      <x:c r="O107" t="str">
+        <x:v>20/07/2026</x:v>
+      </x:c>
+      <x:c r="P107" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="Q107" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="R107" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="S107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T107" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>Paolo Arauco</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>969714361</x:v>
+      </x:c>
+      <x:c r="D108" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F108" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G108" t="str">
+        <x:v>Paolo Arauco</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>71454737</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>51969714361</x:v>
+      </x:c>
+      <x:c r="J108" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L108" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M108" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N108" t="str">
+        <x:v>24/06/2026</x:v>
+      </x:c>
+      <x:c r="O108" t="str">
+        <x:v>26/06/2026</x:v>
+      </x:c>
+      <x:c r="P108" t="str">
+        <x:v>11/07/2026</x:v>
+      </x:c>
+      <x:c r="Q108" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R108" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T108" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>Paolo Arauco</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>969714361</x:v>
+      </x:c>
+      <x:c r="D109" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F109" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G109" t="str">
+        <x:v>Paolo Arauco</x:v>
+      </x:c>
+      <x:c r="H109" t="str">
+        <x:v>71454737</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>969714361</x:v>
+      </x:c>
+      <x:c r="J109" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L109" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M109" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N109" t="str">
+        <x:v>08/07/2026</x:v>
+      </x:c>
+      <x:c r="O109" t="str">
+        <x:v>10/07/2026</x:v>
+      </x:c>
+      <x:c r="P109" t="str">
+        <x:v>09/08/2026</x:v>
+      </x:c>
+      <x:c r="Q109" t="n">
+        <x:v>3029</x:v>
+      </x:c>
+      <x:c r="R109" t="n">
+        <x:v>3029</x:v>
+      </x:c>
+      <x:c r="S109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T109" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>Eduardo Teran</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>51949429958</x:v>
+      </x:c>
+      <x:c r="D110" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F110" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G110" t="str">
+        <x:v>Eduardo Teran</x:v>
+      </x:c>
+      <x:c r="H110" t="str">
+        <x:v>10439108</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>51949429958</x:v>
+      </x:c>
+      <x:c r="J110" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L110" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M110" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N110" t="str">
+        <x:v>24/06/2026</x:v>
+      </x:c>
+      <x:c r="O110" t="str">
+        <x:v>24/06/2026</x:v>
+      </x:c>
+      <x:c r="P110" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="Q110" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R110" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T110" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>Eduardo Teran</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>51949429958</x:v>
+      </x:c>
+      <x:c r="D111" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F111" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G111" t="str">
+        <x:v>Eduardo Teran</x:v>
+      </x:c>
+      <x:c r="H111" t="str">
+        <x:v>10439108</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>51949429958</x:v>
+      </x:c>
+      <x:c r="J111" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L111" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M111" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N111" t="str">
+        <x:v>05/08/2026</x:v>
+      </x:c>
+      <x:c r="O111" t="str">
+        <x:v>05/08/2026</x:v>
+      </x:c>
+      <x:c r="P111" t="str">
+        <x:v>06/08/2026</x:v>
+      </x:c>
+      <x:c r="Q111" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="R111" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="S111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T111" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>Junio 2026</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>Mayte Carolina Pachas Paulino</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>51995551847</x:v>
+      </x:c>
+      <x:c r="D112" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F112" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G112" t="str">
+        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
+      </x:c>
+      <x:c r="H112" t="str">
+        <x:v>47665207</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>51995551847</x:v>
+      </x:c>
+      <x:c r="J112" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L112" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M112" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N112" t="str">
+        <x:v>27/06/2026</x:v>
+      </x:c>
+      <x:c r="O112" t="str">
+        <x:v>27/06/2026</x:v>
+      </x:c>
+      <x:c r="P112" t="str">
+        <x:v>12/07/2026</x:v>
+      </x:c>
+      <x:c r="Q112" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R112" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T112" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>999459492</x:v>
+      </x:c>
+      <x:c r="D113" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>10374186</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>999459492</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L113" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N113" t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c r="O113" t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c r="P113" t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c r="Q113" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R113" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T113" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="D114" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>Web</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>76397222</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L114" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N114" t="str">
+        <x:v>02/07/2026</x:v>
+      </x:c>
+      <x:c r="O114" t="str">
+        <x:v>02/07/2026</x:v>
+      </x:c>
+      <x:c r="P114" t="str">
+        <x:v>17/07/2026</x:v>
+      </x:c>
+      <x:c r="Q114" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R114" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T114" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="D115" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>Web</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>Nathaly Belapatiño</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>76397222</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>993879277</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>15/07/2026</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>15/07/2026</x:v>
+      </x:c>
+      <x:c r="P115" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="Q115" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="R115" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="S115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T115" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>Sve Chang</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>986185776</x:v>
+      </x:c>
+      <x:c r="D116" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>SVE CHANG</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>78007264</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>51 986 185 776</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>03/07/2026</x:v>
+      </x:c>
+      <x:c r="P116" t="str">
+        <x:v>18/07/2026</x:v>
+      </x:c>
+      <x:c r="Q116" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R116" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T116" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>940219366</x:v>
+      </x:c>
+      <x:c r="D117" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>45267059</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>940 219 366</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>06/07/2026</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>06/07/2026</x:v>
+      </x:c>
+      <x:c r="P117" t="str">
+        <x:v>05/08/2026</x:v>
+      </x:c>
+      <x:c r="Q117" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R117" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T117" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>940219366</x:v>
+      </x:c>
+      <x:c r="D118" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>Carolina Hiraoka</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>45267059</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>940 219 366</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>03/08/2026</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>03/08/2026</x:v>
+      </x:c>
+      <x:c r="P118" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="Q118" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R118" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T118" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>941568528</x:v>
+      </x:c>
+      <x:c r="D119" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>009248655</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>51941568528</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L119" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N119" t="str">
+        <x:v>13/07/2026</x:v>
+      </x:c>
+      <x:c r="O119" t="str">
+        <x:v>13/07/2026</x:v>
+      </x:c>
+      <x:c r="P119" t="str">
+        <x:v>28/07/2026</x:v>
+      </x:c>
+      <x:c r="Q119" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R119" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T119" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>941568528</x:v>
+      </x:c>
+      <x:c r="D120" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>Diego Mariño</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>009248655</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>51941568528</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L120" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N120" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="O120" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="P120" t="str">
+        <x:v>22/08/2026</x:v>
+      </x:c>
+      <x:c r="Q120" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="R120" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="S120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T120" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Marcela Noblecilla</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>998678319</x:v>
+      </x:c>
+      <x:c r="D121" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>10058157</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>51998 678 319</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L121" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M121" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N121" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="O121" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="P121" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="Q121" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R121" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T121" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Marcela Noblecilla</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>998678319</x:v>
+      </x:c>
+      <x:c r="D122" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>10058157</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>51998 678 319</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L122" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N122" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="O122" t="str">
+        <x:v>23/07/2026</x:v>
+      </x:c>
+      <x:c r="P122" t="str">
+        <x:v>07/08/2026</x:v>
+      </x:c>
+      <x:c r="Q122" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R122" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T122" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>992978868</x:v>
+      </x:c>
+      <x:c r="D123" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F123" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G123" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="H123" t="str">
+        <x:v>09339021</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>51992978868</x:v>
+      </x:c>
+      <x:c r="J123" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L123" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M123" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N123" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="O123" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="P123" t="str">
+        <x:v>25/07/2026</x:v>
+      </x:c>
+      <x:c r="Q123" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R123" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T123" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>992978868</x:v>
+      </x:c>
+      <x:c r="D124" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>09339021</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>51992978868</x:v>
+      </x:c>
+      <x:c r="J124" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L124" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M124" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N124" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="O124" t="str">
+        <x:v>24/07/2026</x:v>
+      </x:c>
+      <x:c r="P124" t="str">
+        <x:v>08/08/2026</x:v>
+      </x:c>
+      <x:c r="Q124" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R124" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T124" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>992978868</x:v>
+      </x:c>
+      <x:c r="D125" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F125" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>Rocio Cespedes</x:v>
+      </x:c>
+      <x:c r="H125" t="str">
+        <x:v>09339021</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>51992978868</x:v>
+      </x:c>
+      <x:c r="J125" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L125" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M125" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N125" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="O125" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="P125" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="Q125" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R125" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T125" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Jacqueline Idiaquez</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>997512348</x:v>
+      </x:c>
+      <x:c r="D126" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F126" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G126" t="str">
+        <x:v>Jacqueline Idiaquez</x:v>
+      </x:c>
+      <x:c r="H126" t="str">
+        <x:v>09673494</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>997 512 348</x:v>
+      </x:c>
+      <x:c r="J126" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L126" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M126" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N126" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="O126" t="str">
+        <x:v>30/07/2026</x:v>
+      </x:c>
+      <x:c r="P126" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="Q126" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="R126" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="S126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T126" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>Julio 2026</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Lylian Leon</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>996500716</x:v>
+      </x:c>
+      <x:c r="D127" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
+      <x:c r="F127" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G127" t="str">
+        <x:v>Lylian León</x:v>
+      </x:c>
+      <x:c r="H127" t="str">
+        <x:v>07619479</x:v>
+      </x:c>
+      <x:c r="I127" t="str">
+        <x:v>996500716</x:v>
+      </x:c>
+      <x:c r="J127" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L127" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M127" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N127" t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c r="O127" t="str">
+        <x:v>31/07/2026</x:v>
+      </x:c>
+      <x:c r="P127" t="str">
+        <x:v>15/08/2026</x:v>
+      </x:c>
+      <x:c r="Q127" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R127" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S127" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T127" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Karina Saavedra</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>984609397</x:v>
+      </x:c>
+      <x:c r="D128" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E128" t="str"/>
+      <x:c r="F128" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G128" t="str">
+        <x:v>Karina Saavedra Zarria</x:v>
+      </x:c>
+      <x:c r="H128" t="str">
+        <x:v>07628122</x:v>
+      </x:c>
+      <x:c r="I128" t="str">
+        <x:v>51984609397</x:v>
+      </x:c>
+      <x:c r="J128" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L128" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M128" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N128" t="str">
+        <x:v>10/08/2026</x:v>
+      </x:c>
+      <x:c r="O128" t="str">
+        <x:v>10/08/2026</x:v>
+      </x:c>
+      <x:c r="P128" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="Q128" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R128" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T128" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>977648321</x:v>
+      </x:c>
+      <x:c r="D129" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F129" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G129" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="H129" t="str">
+        <x:v>40154559</x:v>
+      </x:c>
+      <x:c r="I129" t="str">
+        <x:v>51977648321</x:v>
+      </x:c>
+      <x:c r="J129" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L129" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M129" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N129" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="O129" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="P129" t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c r="Q129" t="n">
+        <x:v>1385</x:v>
+      </x:c>
+      <x:c r="R129" t="n">
+        <x:v>1385</x:v>
+      </x:c>
+      <x:c r="S129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T129" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>977648321</x:v>
+      </x:c>
+      <x:c r="D130" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F130" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G130" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="H130" t="str">
+        <x:v>40154559</x:v>
+      </x:c>
+      <x:c r="I130" t="str">
+        <x:v>51977648321</x:v>
+      </x:c>
+      <x:c r="J130" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L130" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M130" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N130" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="O130" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="P130" t="str">
+        <x:v>13/08/2026</x:v>
+      </x:c>
+      <x:c r="Q130" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R130" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S130" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T130" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>977648321</x:v>
+      </x:c>
+      <x:c r="D131" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F131" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G131" t="str">
+        <x:v>Sandra Palomino</x:v>
+      </x:c>
+      <x:c r="H131" t="str">
+        <x:v>40154559</x:v>
+      </x:c>
+      <x:c r="I131" t="str">
+        <x:v>51977648321</x:v>
+      </x:c>
+      <x:c r="J131" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K131" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L131" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M131" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N131" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="O131" t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c r="P131" t="str">
+        <x:v>27/08/2026</x:v>
+      </x:c>
+      <x:c r="Q131" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R131" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T131" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>Jeanne Goncalvez</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>2022790015</x:v>
+      </x:c>
+      <x:c r="D132" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F132" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G132" t="str">
+        <x:v>JEANNE GONCALVEZ</x:v>
+      </x:c>
+      <x:c r="H132" t="str">
+        <x:v>20230943</x:v>
+      </x:c>
+      <x:c r="I132" t="str">
+        <x:v>51+1 (202) 279-0015</x:v>
+      </x:c>
+      <x:c r="J132" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K132" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L132" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M132" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N132" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O132" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P132" t="str">
+        <x:v>15/08/2026</x:v>
+      </x:c>
+      <x:c r="Q132" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R132" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T132" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>Jeanne Goncalvez</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>2022790015</x:v>
+      </x:c>
+      <x:c r="D133" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F133" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G133" t="str">
+        <x:v>JEANNE GONCALVEZ</x:v>
+      </x:c>
+      <x:c r="H133" t="str">
+        <x:v>20230943</x:v>
+      </x:c>
+      <x:c r="I133" t="str">
+        <x:v>51+1 (202) 279-0015</x:v>
+      </x:c>
+      <x:c r="J133" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K133" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L133" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M133" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N133" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O133" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P133" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="Q133" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R133" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S133" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T133" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D134" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G134" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H134" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J134" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K134" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L134" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O134" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P134" t="str">
+        <x:v>15/08/2026</x:v>
+      </x:c>
+      <x:c r="Q134" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R134" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T134" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D135" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J135" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K135" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L135" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M135" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O135" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P135" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="Q135" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R135" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T135" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>989174565</x:v>
+      </x:c>
+      <x:c r="D136" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="E136" t="str"/>
+      <x:c r="F136" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G136" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="H136" t="str">
+        <x:v>09752091</x:v>
+      </x:c>
+      <x:c r="I136" t="str">
+        <x:v>51989174565</x:v>
+      </x:c>
+      <x:c r="J136" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K136" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L136" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M136" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N136" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O136" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P136" t="str">
+        <x:v>17/09/2026</x:v>
+      </x:c>
+      <x:c r="Q136" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="R136" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="S136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T136" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>Maribel Toledo</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>949604263</x:v>
+      </x:c>
+      <x:c r="D137" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E137" t="str"/>
+      <x:c r="F137" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>MARIBEL TOLEDO</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>10477277</x:v>
+      </x:c>
+      <x:c r="I137" t="str">
+        <x:v>51949604263</x:v>
+      </x:c>
+      <x:c r="J137" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K137" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L137" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M137" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N137" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O137" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P137" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="Q137" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R137" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T137" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>Maribel Toledo</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>949604263</x:v>
+      </x:c>
+      <x:c r="D138" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E138" t="str"/>
+      <x:c r="F138" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G138" t="str">
+        <x:v>MARIBEL TOLEDO</x:v>
+      </x:c>
+      <x:c r="H138" t="str">
+        <x:v>10477277</x:v>
+      </x:c>
+      <x:c r="I138" t="str">
+        <x:v>51949604263</x:v>
+      </x:c>
+      <x:c r="J138" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K138" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L138" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M138" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N138" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O138" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P138" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="Q138" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R138" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T138" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="D139" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E139" t="str"/>
+      <x:c r="F139" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G139" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="H139" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="I139" t="str">
+        <x:v>10545751</x:v>
+      </x:c>
+      <x:c r="J139" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K139" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L139" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M139" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N139" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="O139" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="P139" t="str">
+        <x:v>20/08/2026</x:v>
+      </x:c>
+      <x:c r="Q139" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R139" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T139" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="D140" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E140" t="str"/>
+      <x:c r="F140" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>10545751</x:v>
+      </x:c>
+      <x:c r="J140" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L140" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="P140" t="str">
+        <x:v>03/09/2026</x:v>
+      </x:c>
+      <x:c r="Q140" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R140" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T140" t="str">
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
+++ b/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="R1682423bf02e443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="R4522fae2c4a44cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="Rf7e44d405a0b4dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="Rc8467125fa9a4597"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -415,22 +415,22 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="n">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B4" s="12" t="n">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C4" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="12" t="n">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>132</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F4" s="12" t="n">
-        <x:v>171884</x:v>
+        <x:v>191884</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1981,28 +1981,28 @@
         <x:v>959237010</x:v>
       </x:c>
       <x:c r="J34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K34" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K34" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L34" t="n">
-        <x:v>5198</x:v>
+        <x:v>6187</x:v>
       </x:c>
       <x:c r="M34" t="n">
-        <x:v>5198</x:v>
+        <x:v>6187</x:v>
       </x:c>
       <x:c r="N34" t="str">
         <x:v>27/04/2026</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="P34" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R34" t="n">
         <x:v>0</x:v>
@@ -2095,28 +2095,28 @@
         <x:v>986645733</x:v>
       </x:c>
       <x:c r="J36" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K36" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K36" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L36" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="M36" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="N36" t="str">
         <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="P36" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R36" t="n">
         <x:v>0</x:v>
@@ -2608,28 +2608,28 @@
         <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K45" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L45" t="n">
-        <x:v>1989</x:v>
+        <x:v>3158</x:v>
       </x:c>
       <x:c r="M45" t="n">
-        <x:v>1989</x:v>
+        <x:v>3158</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="P45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q45" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R45" t="n">
         <x:v>0</x:v>
@@ -2950,28 +2950,28 @@
         <x:v>999459492</x:v>
       </x:c>
       <x:c r="J51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K51" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L51" t="n">
-        <x:v>2219</x:v>
+        <x:v>4235</x:v>
       </x:c>
       <x:c r="M51" t="n">
-        <x:v>2219</x:v>
+        <x:v>4235</x:v>
       </x:c>
       <x:c r="N51" t="str">
         <x:v>01/07/2026</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>01/07/2026</x:v>
+        <x:v>21/08/2026</x:v>
       </x:c>
       <x:c r="P51" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q51" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R51" t="n">
         <x:v>0</x:v>
@@ -3121,28 +3121,28 @@
         <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J54" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K54" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L54" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="M54" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="N54" t="str">
         <x:v>06/07/2026</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>03/08/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="P54" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q54" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R54" t="n">
         <x:v>0</x:v>
@@ -3349,28 +3349,28 @@
         <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K58" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L58" t="n">
-        <x:v>2219</x:v>
+        <x:v>4438</x:v>
       </x:c>
       <x:c r="M58" t="n">
-        <x:v>2219</x:v>
+        <x:v>4438</x:v>
       </x:c>
       <x:c r="N58" t="str">
         <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="P58" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q58" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R58" t="n">
         <x:v>0</x:v>
@@ -3575,28 +3575,28 @@
         <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J62" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K62" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L62" t="n">
-        <x:v>1900</x:v>
+        <x:v>3285</x:v>
       </x:c>
       <x:c r="M62" t="n">
-        <x:v>1900</x:v>
+        <x:v>3285</x:v>
       </x:c>
       <x:c r="N62" t="str">
         <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O62" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>26/08/2026</x:v>
       </x:c>
       <x:c r="P62" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q62" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R62" t="n">
         <x:v>0</x:v>
@@ -3632,28 +3632,28 @@
         <x:v>51+1 (202) 560-0320</x:v>
       </x:c>
       <x:c r="J63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K63" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K63" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="L63" t="n">
-        <x:v>1900</x:v>
+        <x:v>4784</x:v>
       </x:c>
       <x:c r="M63" t="n">
-        <x:v>1900</x:v>
+        <x:v>4784</x:v>
       </x:c>
       <x:c r="N63" t="str">
         <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O63" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>26/08/2026</x:v>
       </x:c>
       <x:c r="P63" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q63" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R63" t="n">
         <x:v>0</x:v>
@@ -3824,6 +3824,234 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Sandra Contreras</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>948067720</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>SANDRA CONTRERAS</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>07465701</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>51948706868</x:v>
+      </x:c>
+      <x:c r="J67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L67" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M67" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>24/08/2026</x:v>
+      </x:c>
+      <x:c r="O67" t="str">
+        <x:v>24/08/2026</x:v>
+      </x:c>
+      <x:c r="P67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>Federico Leon</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>948687720</x:v>
+      </x:c>
+      <x:c r="D68" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>Federico Leon</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>07869853</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>51994687720</x:v>
+      </x:c>
+      <x:c r="J68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L68" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M68" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="O68" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="P68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>Daniela Door</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>997959393</x:v>
+      </x:c>
+      <x:c r="D69" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G69" t="str">
+        <x:v>Daniela Door</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>07761819</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>51997595393</x:v>
+      </x:c>
+      <x:c r="J69" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M69" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c r="O69" t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c r="P69" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>968765284</x:v>
+      </x:c>
+      <x:c r="D70" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G70" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>21533929</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>51968 765 284</x:v>
+      </x:c>
+      <x:c r="J70" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K70" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L70" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="M70" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="N70" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="O70" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="P70" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q70" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R70" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S70" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8641,64 +8869,64 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>Mayo 2026</x:v>
+        <x:v>Abril 2026</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>Mathias Brivio</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>999197080</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="D79" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E79" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F79" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>Mathias Brivio</x:v>
+        <x:v>Luis Rodriguez</x:v>
       </x:c>
       <x:c r="H79" t="str">
-        <x:v>10268598</x:v>
+        <x:v>40783552</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>999197080</x:v>
+        <x:v>959237010</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L79" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M79" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N79" t="str">
-        <x:v>12/05/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="O79" t="str">
-        <x:v>12/05/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="P79" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>19/09/2026</x:v>
       </x:c>
       <x:c r="Q79" t="n">
-        <x:v>2219</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R79" t="n">
-        <x:v>2219</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S79" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T79" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8706,28 +8934,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mathias Brivio</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>986645733</x:v>
+        <x:v>999197080</x:v>
       </x:c>
       <x:c r="D80" t="n">
         <x:v>2219</x:v>
       </x:c>
       <x:c r="E80" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F80" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G80" t="str">
-        <x:v>Fernando Chocano</x:v>
+        <x:v>Mathias Brivio</x:v>
       </x:c>
       <x:c r="H80" t="str">
-        <x:v>08217010</x:v>
+        <x:v>10268598</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>986645733</x:v>
+        <x:v>999197080</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Nuevo</x:v>
@@ -8742,13 +8970,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N80" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>12/05/2026</x:v>
       </x:c>
       <x:c r="O80" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>12/05/2026</x:v>
       </x:c>
       <x:c r="P80" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="Q80" t="n">
         <x:v>2219</x:v>
@@ -8792,10 +9020,10 @@
         <x:v>986645733</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L81" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -8804,13 +9032,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N81" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O81" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="P81" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="Q81" t="n">
         <x:v>2219</x:v>
@@ -8822,7 +9050,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T81" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -8830,61 +9058,61 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>Javier Bracco Puch</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>945678019</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="D82" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E82" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F82" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G82" t="str">
-        <x:v>Javier Edgardo Bracco Puch</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="H82" t="str">
-        <x:v>43226753</x:v>
+        <x:v>08217010</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>51945678019</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="J82" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L82" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M82" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N82" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O82" t="str">
-        <x:v>18/05/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="P82" t="str">
-        <x:v>02/06/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="Q82" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R82" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S82" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T82" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -8892,28 +9120,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>Javier Bracco Puch</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>945678019</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="D83" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F83" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G83" t="str">
-        <x:v>Javier Edgardo Bracco Puch</x:v>
+        <x:v>Fernando Chocano</x:v>
       </x:c>
       <x:c r="H83" t="str">
-        <x:v>43226753</x:v>
+        <x:v>08217010</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>51945678019</x:v>
+        <x:v>986645733</x:v>
       </x:c>
       <x:c r="J83" t="str">
         <x:v>Renovacion</x:v>
@@ -8922,31 +9150,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M83" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N83" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="O83" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="P83" t="str">
-        <x:v>04/07/2026</x:v>
+        <x:v>19/09/2026</x:v>
       </x:c>
       <x:c r="Q83" t="n">
-        <x:v>1169</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R83" t="n">
-        <x:v>1169</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S83" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T83" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -8975,40 +9203,40 @@
         <x:v>43226753</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>945678019</x:v>
+        <x:v>51945678019</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L84" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M84" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N84" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="O84" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>18/05/2026</x:v>
       </x:c>
       <x:c r="P84" t="str">
-        <x:v>09/08/2026</x:v>
+        <x:v>02/06/2026</x:v>
       </x:c>
       <x:c r="Q84" t="n">
-        <x:v>1169</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R84" t="n">
-        <x:v>1169</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S84" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T84" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -9016,13 +9244,13 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Javier Bracco Puch</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>998119233</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="D85" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E85" t="str">
         <x:v>DM</x:v>
@@ -9031,46 +9259,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Javier Edgardo Bracco Puch</x:v>
       </x:c>
       <x:c r="H85" t="str">
-        <x:v>09399588</x:v>
+        <x:v>43226753</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>998119233</x:v>
+        <x:v>51945678019</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M85" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N85" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="O85" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>04/06/2026</x:v>
       </x:c>
       <x:c r="P85" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>04/07/2026</x:v>
       </x:c>
       <x:c r="Q85" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R85" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S85" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T85" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -9078,13 +9306,13 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Javier Bracco Puch</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>998119233</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="D86" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E86" t="str">
         <x:v>DM</x:v>
@@ -9093,13 +9321,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G86" t="str">
-        <x:v>Jose Espinoza</x:v>
+        <x:v>Javier Edgardo Bracco Puch</x:v>
       </x:c>
       <x:c r="H86" t="str">
-        <x:v>09399588</x:v>
+        <x:v>43226753</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>998119233</x:v>
+        <x:v>945678019</x:v>
       </x:c>
       <x:c r="J86" t="str">
         <x:v>Renovacion</x:v>
@@ -9108,25 +9336,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L86" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M86" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N86" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="O86" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P86" t="str">
-        <x:v>26/07/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q86" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R86" t="n">
-        <x:v>2219</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S86" t="n">
         <x:v>0</x:v>
@@ -9164,10 +9392,10 @@
         <x:v>998119233</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L87" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -9176,25 +9404,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N87" t="str">
-        <x:v>04/08/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O87" t="str">
-        <x:v>04/08/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="P87" t="str">
-        <x:v>03/09/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="Q87" t="n">
-        <x:v>3029</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R87" t="n">
-        <x:v>3029</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S87" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T87" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -9202,61 +9430,61 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>997511543</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="D88" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E88" t="str">
-        <x:v>Digital</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F88" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G88" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="H88" t="str">
-        <x:v>10223240</x:v>
+        <x:v>09399588</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>51997511543</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L88" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M88" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N88" t="str">
-        <x:v>25/05/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="O88" t="str">
-        <x:v>02/06/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="P88" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>26/07/2026</x:v>
       </x:c>
       <x:c r="Q88" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R88" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S88" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T88" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -9264,28 +9492,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>997511543</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="D89" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E89" t="str">
-        <x:v>Digital</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F89" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G89" t="str">
-        <x:v>Fernando Razeto</x:v>
+        <x:v>Jose Espinoza</x:v>
       </x:c>
       <x:c r="H89" t="str">
-        <x:v>10223240</x:v>
+        <x:v>09399588</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>51997511543</x:v>
+        <x:v>998119233</x:v>
       </x:c>
       <x:c r="J89" t="str">
         <x:v>Renovacion</x:v>
@@ -9300,19 +9528,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N89" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="O89" t="str">
-        <x:v>11/06/2026</x:v>
+        <x:v>04/08/2026</x:v>
       </x:c>
       <x:c r="P89" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>03/09/2026</x:v>
       </x:c>
       <x:c r="Q89" t="n">
-        <x:v>2219</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R89" t="n">
-        <x:v>2219</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S89" t="n">
         <x:v>0</x:v>
@@ -9326,28 +9554,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>951329266</x:v>
+        <x:v>997511543</x:v>
       </x:c>
       <x:c r="D90" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E90" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F90" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="H90" t="str">
-        <x:v>10474396</x:v>
+        <x:v>10223240</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>51951329266</x:v>
+        <x:v>51997511543</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>Nuevo</x:v>
@@ -9362,13 +9590,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N90" t="str">
-        <x:v>29/05/2026</x:v>
+        <x:v>25/05/2026</x:v>
       </x:c>
       <x:c r="O90" t="str">
-        <x:v>29/05/2026</x:v>
+        <x:v>02/06/2026</x:v>
       </x:c>
       <x:c r="P90" t="str">
-        <x:v>16/07/2026</x:v>
+        <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="Q90" t="n">
         <x:v>1000</x:v>
@@ -9388,28 +9616,28 @@
         <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>951329266</x:v>
+        <x:v>997511543</x:v>
       </x:c>
       <x:c r="D91" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F91" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G91" t="str">
-        <x:v>Claudia Namizato</x:v>
+        <x:v>Fernando Razeto</x:v>
       </x:c>
       <x:c r="H91" t="str">
-        <x:v>10474396</x:v>
+        <x:v>10223240</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>51951329266</x:v>
+        <x:v>51997511543</x:v>
       </x:c>
       <x:c r="J91" t="str">
         <x:v>Renovacion</x:v>
@@ -9424,13 +9652,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N91" t="str">
-        <x:v>08/07/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="O91" t="str">
-        <x:v>08/07/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="P91" t="str">
-        <x:v>07/08/2026</x:v>
+        <x:v>11/07/2026</x:v>
       </x:c>
       <x:c r="Q91" t="n">
         <x:v>2219</x:v>
@@ -9447,37 +9675,37 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>955098767</x:v>
+        <x:v>951329266</x:v>
       </x:c>
       <x:c r="D92" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E92" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F92" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G92" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="H92" t="str">
-        <x:v>07816623</x:v>
+        <x:v>10474396</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>955098767</x:v>
+        <x:v>51951329266</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L92" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -9486,13 +9714,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N92" t="str">
-        <x:v>04/06/2026</x:v>
+        <x:v>29/05/2026</x:v>
       </x:c>
       <x:c r="O92" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>29/05/2026</x:v>
       </x:c>
       <x:c r="P92" t="str">
-        <x:v>23/06/2026</x:v>
+        <x:v>16/07/2026</x:v>
       </x:c>
       <x:c r="Q92" t="n">
         <x:v>1000</x:v>
@@ -9509,31 +9737,31 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>Junio 2026</x:v>
+        <x:v>Mayo 2026</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>955098767</x:v>
+        <x:v>951329266</x:v>
       </x:c>
       <x:c r="D93" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E93" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F93" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G93" t="str">
-        <x:v>Hernan Bello</x:v>
+        <x:v>Claudia Namizato</x:v>
       </x:c>
       <x:c r="H93" t="str">
-        <x:v>07816623</x:v>
+        <x:v>10474396</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>955098767</x:v>
+        <x:v>51951329266</x:v>
       </x:c>
       <x:c r="J93" t="str">
         <x:v>Renovacion</x:v>
@@ -9548,13 +9776,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N93" t="str">
+        <x:v>08/07/2026</x:v>
+      </x:c>
+      <x:c r="O93" t="str">
+        <x:v>08/07/2026</x:v>
+      </x:c>
+      <x:c r="P93" t="str">
         <x:v>07/08/2026</x:v>
-      </x:c>
-      <x:c r="O93" t="str">
-        <x:v>07/08/2026</x:v>
-      </x:c>
-      <x:c r="P93" t="str">
-        <x:v>06/09/2026</x:v>
       </x:c>
       <x:c r="Q93" t="n">
         <x:v>2219</x:v>
@@ -9574,10 +9802,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>942126985</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="D94" t="n">
         <x:v>1900</x:v>
@@ -9589,13 +9817,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G94" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="H94" t="str">
-        <x:v>07816622</x:v>
+        <x:v>07816623</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>51942126985</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="J94" t="str">
         <x:v>Nuevo</x:v>
@@ -9636,10 +9864,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>942126985</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="D95" t="n">
         <x:v>1900</x:v>
@@ -9651,13 +9879,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G95" t="str">
-        <x:v>Martha Velez</x:v>
+        <x:v>Hernan Bello</x:v>
       </x:c>
       <x:c r="H95" t="str">
-        <x:v>07816622</x:v>
+        <x:v>07816623</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>942126985</x:v>
+        <x:v>955098767</x:v>
       </x:c>
       <x:c r="J95" t="str">
         <x:v>Renovacion</x:v>
@@ -9672,13 +9900,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N95" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="O95" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="P95" t="str">
-        <x:v>23/08/2026</x:v>
+        <x:v>06/09/2026</x:v>
       </x:c>
       <x:c r="Q95" t="n">
         <x:v>2219</x:v>
@@ -9698,28 +9926,28 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Martha Velez</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>983343707</x:v>
+        <x:v>942126985</x:v>
       </x:c>
       <x:c r="D96" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E96" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F96" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G96" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Martha Velez</x:v>
       </x:c>
       <x:c r="H96" t="str">
-        <x:v>42265772</x:v>
+        <x:v>07816622</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>983343707</x:v>
+        <x:v>51942126985</x:v>
       </x:c>
       <x:c r="J96" t="str">
         <x:v>Nuevo</x:v>
@@ -9734,13 +9962,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N96" t="str">
+        <x:v>04/06/2026</x:v>
+      </x:c>
+      <x:c r="O96" t="str">
         <x:v>08/06/2026</x:v>
       </x:c>
-      <x:c r="O96" t="str">
-        <x:v>11/06/2026</x:v>
-      </x:c>
       <x:c r="P96" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>23/06/2026</x:v>
       </x:c>
       <x:c r="Q96" t="n">
         <x:v>1000</x:v>
@@ -9760,61 +9988,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Martha Velez</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>983343707</x:v>
+        <x:v>942126985</x:v>
       </x:c>
       <x:c r="D97" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E97" t="str">
-        <x:v>Instagram</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F97" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G97" t="str">
-        <x:v>Renzo Sotomayor Diaz</x:v>
+        <x:v>Martha Velez</x:v>
       </x:c>
       <x:c r="H97" t="str">
-        <x:v>42265772</x:v>
+        <x:v>07816622</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>983343707</x:v>
+        <x:v>942126985</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L97" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M97" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N97" t="str">
-        <x:v>08/06/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="O97" t="str">
-        <x:v>18/06/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P97" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>23/08/2026</x:v>
       </x:c>
       <x:c r="Q97" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R97" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S97" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T97" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -9822,34 +10050,34 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Renzo Sotomayor Diaz</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>945127771</x:v>
+        <x:v>983343707</x:v>
       </x:c>
       <x:c r="D98" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E98" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F98" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G98" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Renzo Sotomayor Diaz</x:v>
       </x:c>
       <x:c r="H98" t="str">
-        <x:v>41687688</x:v>
+        <x:v>42265772</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>51945127771</x:v>
+        <x:v>983343707</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L98" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -9858,13 +10086,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N98" t="str">
-        <x:v>16/06/2026</x:v>
+        <x:v>08/06/2026</x:v>
       </x:c>
       <x:c r="O98" t="str">
-        <x:v>18/06/2026</x:v>
+        <x:v>11/06/2026</x:v>
       </x:c>
       <x:c r="P98" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="Q98" t="n">
         <x:v>1000</x:v>
@@ -9884,61 +10112,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Renzo Sotomayor Diaz</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>945127771</x:v>
+        <x:v>983343707</x:v>
       </x:c>
       <x:c r="D99" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E99" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Instagram</x:v>
       </x:c>
       <x:c r="F99" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G99" t="str">
-        <x:v>Andres San Miguel</x:v>
+        <x:v>Renzo Sotomayor Diaz</x:v>
       </x:c>
       <x:c r="H99" t="str">
-        <x:v>41687688</x:v>
+        <x:v>42265772</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>51945127771</x:v>
+        <x:v>983343707</x:v>
       </x:c>
       <x:c r="J99" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L99" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M99" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N99" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>08/06/2026</x:v>
       </x:c>
       <x:c r="O99" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>18/06/2026</x:v>
       </x:c>
       <x:c r="P99" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="Q99" t="n">
-        <x:v>989</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R99" t="n">
-        <x:v>989</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S99" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T99" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -9970,37 +10198,37 @@
         <x:v>51945127771</x:v>
       </x:c>
       <x:c r="J100" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K100" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L100" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M100" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N100" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>16/06/2026</x:v>
       </x:c>
       <x:c r="O100" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>18/06/2026</x:v>
       </x:c>
       <x:c r="P100" t="str">
-        <x:v>16/08/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="Q100" t="n">
-        <x:v>989</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R100" t="n">
-        <x:v>989</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S100" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T100" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -10044,19 +10272,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N101" t="str">
-        <x:v>07/08/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O101" t="str">
-        <x:v>07/08/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="P101" t="str">
-        <x:v>06/09/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="Q101" t="n">
-        <x:v>1169</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R101" t="n">
-        <x:v>1169</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S101" t="n">
         <x:v>0</x:v>
@@ -10070,10 +10298,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B102" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Andres San Miguel</x:v>
       </x:c>
       <x:c r="C102" t="str">
-        <x:v>955929014</x:v>
+        <x:v>945127771</x:v>
       </x:c>
       <x:c r="D102" t="n">
         <x:v>1900</x:v>
@@ -10085,46 +10313,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G102" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Andres San Miguel</x:v>
       </x:c>
       <x:c r="H102" t="str">
-        <x:v>42816308</x:v>
+        <x:v>41687688</x:v>
       </x:c>
       <x:c r="I102" t="str">
-        <x:v>51955929014</x:v>
+        <x:v>51945127771</x:v>
       </x:c>
       <x:c r="J102" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L102" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M102" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N102" t="str">
-        <x:v>17/06/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="O102" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="P102" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>16/08/2026</x:v>
       </x:c>
       <x:c r="Q102" t="n">
-        <x:v>1000</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R102" t="n">
-        <x:v>1000</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S102" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T102" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -10132,10 +10360,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B103" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Andres San Miguel</x:v>
       </x:c>
       <x:c r="C103" t="str">
-        <x:v>955929014</x:v>
+        <x:v>945127771</x:v>
       </x:c>
       <x:c r="D103" t="n">
         <x:v>1900</x:v>
@@ -10147,13 +10375,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G103" t="str">
-        <x:v>Manuel Montes de Oca</x:v>
+        <x:v>Andres San Miguel</x:v>
       </x:c>
       <x:c r="H103" t="str">
-        <x:v>42816308</x:v>
+        <x:v>41687688</x:v>
       </x:c>
       <x:c r="I103" t="str">
-        <x:v>51955929014</x:v>
+        <x:v>51945127771</x:v>
       </x:c>
       <x:c r="J103" t="str">
         <x:v>Renovacion</x:v>
@@ -10168,19 +10396,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N103" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="O103" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="P103" t="str">
-        <x:v>09/08/2026</x:v>
+        <x:v>06/09/2026</x:v>
       </x:c>
       <x:c r="Q103" t="n">
-        <x:v>989</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R103" t="n">
-        <x:v>989</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S103" t="n">
         <x:v>0</x:v>
@@ -10194,10 +10422,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B104" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="C104" t="str">
-        <x:v>997921230</x:v>
+        <x:v>955929014</x:v>
       </x:c>
       <x:c r="D104" t="n">
         <x:v>1900</x:v>
@@ -10209,13 +10437,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G104" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="H104" t="str">
-        <x:v>08275871</x:v>
+        <x:v>42816308</x:v>
       </x:c>
       <x:c r="I104" t="str">
-        <x:v>51997921230</x:v>
+        <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J104" t="str">
         <x:v>Nuevo</x:v>
@@ -10230,13 +10458,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N104" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="O104" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="P104" t="str">
-        <x:v>04/07/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="Q104" t="n">
         <x:v>1000</x:v>
@@ -10256,10 +10484,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B105" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="C105" t="str">
-        <x:v>997921230</x:v>
+        <x:v>955929014</x:v>
       </x:c>
       <x:c r="D105" t="n">
         <x:v>1900</x:v>
@@ -10271,13 +10499,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G105" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="H105" t="str">
-        <x:v>08275871</x:v>
+        <x:v>42816308</x:v>
       </x:c>
       <x:c r="I105" t="str">
-        <x:v>51997921230</x:v>
+        <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J105" t="str">
         <x:v>Renovacion</x:v>
@@ -10292,19 +10520,19 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N105" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="O105" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P105" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q105" t="n">
-        <x:v>779</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R105" t="n">
-        <x:v>779</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S105" t="n">
         <x:v>0</x:v>
@@ -10318,61 +10546,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B106" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="C106" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>955929014</x:v>
       </x:c>
       <x:c r="D106" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E106" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F106" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G106" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="H106" t="str">
-        <x:v>7770642o</x:v>
+        <x:v>42816308</x:v>
       </x:c>
       <x:c r="I106" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J106" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K106" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L106" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M106" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N106" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="O106" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="P106" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="Q106" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="R106" t="n">
-        <x:v>1000</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="S106" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T106" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -10380,61 +10608,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B107" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Beto Mendez</x:v>
       </x:c>
       <x:c r="C107" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>997921230</x:v>
       </x:c>
       <x:c r="D107" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E107" t="str">
+        <x:v>Linktree</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>Beto Mendez</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>08275871</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>51997921230</x:v>
+      </x:c>
+      <x:c r="J107" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
         <x:v>Digital</x:v>
       </x:c>
-      <x:c r="F107" t="str">
-        <x:v>Telefono</x:v>
-      </x:c>
-      <x:c r="G107" t="str">
-        <x:v>Nadia Gutierrez</x:v>
-      </x:c>
-      <x:c r="H107" t="str">
-        <x:v>7770642o</x:v>
-      </x:c>
-      <x:c r="I107" t="str">
-        <x:v>987504234</x:v>
-      </x:c>
-      <x:c r="J107" t="str">
-        <x:v>Renovacion</x:v>
-      </x:c>
-      <x:c r="K107" t="str">
-        <x:v>Renovacion</x:v>
-      </x:c>
       <x:c r="L107" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M107" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N107" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="O107" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="P107" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>04/07/2026</x:v>
       </x:c>
       <x:c r="Q107" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R107" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S107" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T107" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10442,10 +10670,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B108" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Beto Mendez</x:v>
       </x:c>
       <x:c r="C108" t="str">
-        <x:v>969714361</x:v>
+        <x:v>997921230</x:v>
       </x:c>
       <x:c r="D108" t="n">
         <x:v>1900</x:v>
@@ -10457,46 +10685,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G108" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Beto Mendez</x:v>
       </x:c>
       <x:c r="H108" t="str">
-        <x:v>71454737</x:v>
+        <x:v>08275871</x:v>
       </x:c>
       <x:c r="I108" t="str">
-        <x:v>51969714361</x:v>
+        <x:v>51997921230</x:v>
       </x:c>
       <x:c r="J108" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L108" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M108" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N108" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O108" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="P108" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="Q108" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R108" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S108" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T108" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -10504,61 +10732,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B109" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="C109" t="str">
-        <x:v>969714361</x:v>
+        <x:v>51987504234</x:v>
       </x:c>
       <x:c r="D109" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E109" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F109" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G109" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="H109" t="str">
-        <x:v>71454737</x:v>
+        <x:v>7770642o</x:v>
       </x:c>
       <x:c r="I109" t="str">
-        <x:v>969714361</x:v>
+        <x:v>51987504234</x:v>
       </x:c>
       <x:c r="J109" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K109" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L109" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M109" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N109" t="str">
-        <x:v>08/07/2026</x:v>
+        <x:v>25/06/2026</x:v>
       </x:c>
       <x:c r="O109" t="str">
+        <x:v>25/06/2026</x:v>
+      </x:c>
+      <x:c r="P109" t="str">
         <x:v>10/07/2026</x:v>
       </x:c>
-      <x:c r="P109" t="str">
-        <x:v>09/08/2026</x:v>
-      </x:c>
       <x:c r="Q109" t="n">
-        <x:v>3029</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R109" t="n">
-        <x:v>3029</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S109" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T109" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -10566,61 +10794,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B110" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="C110" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>51987504234</x:v>
       </x:c>
       <x:c r="D110" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E110" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F110" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G110" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="H110" t="str">
-        <x:v>10439108</x:v>
+        <x:v>7770642o</x:v>
       </x:c>
       <x:c r="I110" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>987504234</x:v>
       </x:c>
       <x:c r="J110" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K110" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L110" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M110" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N110" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="O110" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="P110" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="Q110" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R110" t="n">
-        <x:v>2219</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S110" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T110" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -10628,61 +10856,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B111" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="C111" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>969714361</x:v>
       </x:c>
       <x:c r="D111" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E111" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F111" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G111" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="H111" t="str">
-        <x:v>10439108</x:v>
+        <x:v>71454737</x:v>
       </x:c>
       <x:c r="I111" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>51969714361</x:v>
       </x:c>
       <x:c r="J111" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K111" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L111" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M111" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N111" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O111" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="P111" t="str">
-        <x:v>06/08/2026</x:v>
+        <x:v>11/07/2026</x:v>
       </x:c>
       <x:c r="Q111" t="n">
-        <x:v>277</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R111" t="n">
-        <x:v>277</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T111" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -10690,55 +10918,55 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B112" t="str">
-        <x:v>Mayte Carolina Pachas Paulino</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="C112" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>969714361</x:v>
       </x:c>
       <x:c r="D112" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E112" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F112" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="H112" t="str">
-        <x:v>47665207</x:v>
+        <x:v>71454737</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>969714361</x:v>
       </x:c>
       <x:c r="J112" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L112" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M112" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N112" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="O112" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P112" t="str">
-        <x:v>12/07/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q112" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R112" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S112" t="n">
         <x:v>0</x:v>
@@ -10749,31 +10977,31 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="str">
-        <x:v>Julio 2026</x:v>
+        <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B113" t="str">
-        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="C113" t="str">
-        <x:v>999459492</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="D113" t="n">
         <x:v>2219</x:v>
       </x:c>
       <x:c r="E113" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F113" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G113" t="str">
-        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="H113" t="str">
-        <x:v>10374186</x:v>
+        <x:v>10439108</x:v>
       </x:c>
       <x:c r="I113" t="str">
-        <x:v>999459492</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="J113" t="str">
         <x:v>Nuevo</x:v>
@@ -10788,13 +11016,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N113" t="str">
-        <x:v>01/07/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O113" t="str">
-        <x:v>01/07/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="P113" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="Q113" t="n">
         <x:v>2219</x:v>
@@ -10811,120 +11039,120 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="str">
-        <x:v>Julio 2026</x:v>
+        <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B114" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="C114" t="str">
-        <x:v>993879277</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="D114" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E114" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F114" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G114" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="H114" t="str">
-        <x:v>76397222</x:v>
+        <x:v>10439108</x:v>
       </x:c>
       <x:c r="I114" t="str">
-        <x:v>993879277</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="J114" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K114" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L114" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M114" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N114" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="O114" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="P114" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>06/08/2026</x:v>
       </x:c>
       <x:c r="Q114" t="n">
-        <x:v>1000</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="R114" t="n">
-        <x:v>1000</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="S114" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="str">
-        <x:v>Julio 2026</x:v>
+        <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B115" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>Mayte Carolina Pachas Paulino</x:v>
       </x:c>
       <x:c r="C115" t="str">
-        <x:v>993879277</x:v>
+        <x:v>51995551847</x:v>
       </x:c>
       <x:c r="D115" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E115" t="str">
-        <x:v>Web</x:v>
+        <x:v>Mirko</x:v>
       </x:c>
       <x:c r="F115" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G115" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
       </x:c>
       <x:c r="H115" t="str">
-        <x:v>76397222</x:v>
+        <x:v>47665207</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>993879277</x:v>
+        <x:v>51995551847</x:v>
       </x:c>
       <x:c r="J115" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L115" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M115" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N115" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="O115" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="P115" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/07/2026</x:v>
       </x:c>
       <x:c r="Q115" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R115" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S115" t="n">
         <x:v>0</x:v>
@@ -10938,61 +11166,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B116" t="str">
-        <x:v>Sve Chang</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="C116" t="str">
-        <x:v>986185776</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="D116" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E116" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F116" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G116" t="str">
-        <x:v>SVE CHANG</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="H116" t="str">
-        <x:v>78007264</x:v>
+        <x:v>10374186</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>51 986 185 776</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="J116" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L116" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M116" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N116" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>01/07/2026</x:v>
       </x:c>
       <x:c r="O116" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>01/07/2026</x:v>
       </x:c>
       <x:c r="P116" t="str">
-        <x:v>18/07/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="Q116" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R116" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S116" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -11000,61 +11228,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B117" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="C117" t="str">
-        <x:v>940219366</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="D117" t="n">
         <x:v>2219</x:v>
       </x:c>
       <x:c r="E117" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F117" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G117" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="H117" t="str">
-        <x:v>45267059</x:v>
+        <x:v>10374186</x:v>
       </x:c>
       <x:c r="I117" t="str">
-        <x:v>940 219 366</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="J117" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K117" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L117" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M117" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N117" t="str">
-        <x:v>06/07/2026</x:v>
+        <x:v>21/08/2026</x:v>
       </x:c>
       <x:c r="O117" t="str">
-        <x:v>06/07/2026</x:v>
+        <x:v>21/08/2026</x:v>
       </x:c>
       <x:c r="P117" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>14/09/2026</x:v>
       </x:c>
       <x:c r="Q117" t="n">
-        <x:v>2219</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="R117" t="n">
-        <x:v>2219</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="S117" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -11062,61 +11290,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B118" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="C118" t="str">
-        <x:v>940219366</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="D118" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E118" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F118" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G118" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="H118" t="str">
-        <x:v>45267059</x:v>
+        <x:v>76397222</x:v>
       </x:c>
       <x:c r="I118" t="str">
-        <x:v>940 219 366</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="J118" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K118" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L118" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M118" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N118" t="str">
-        <x:v>03/08/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="O118" t="str">
-        <x:v>03/08/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="P118" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="Q118" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R118" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S118" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -11124,61 +11352,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B119" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="C119" t="str">
-        <x:v>941568528</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="D119" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E119" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F119" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G119" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="H119" t="str">
-        <x:v>009248655</x:v>
+        <x:v>76397222</x:v>
       </x:c>
       <x:c r="I119" t="str">
-        <x:v>51941568528</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="J119" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K119" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L119" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M119" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N119" t="str">
-        <x:v>13/07/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="O119" t="str">
-        <x:v>13/07/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="P119" t="str">
-        <x:v>28/07/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="Q119" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R119" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S119" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T119" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -11186,10 +11414,10 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B120" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>Sve Chang</x:v>
       </x:c>
       <x:c r="C120" t="str">
-        <x:v>941568528</x:v>
+        <x:v>986185776</x:v>
       </x:c>
       <x:c r="D120" t="n">
         <x:v>1900</x:v>
@@ -11201,40 +11429,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G120" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>SVE CHANG</x:v>
       </x:c>
       <x:c r="H120" t="str">
-        <x:v>009248655</x:v>
+        <x:v>78007264</x:v>
       </x:c>
       <x:c r="I120" t="str">
-        <x:v>51941568528</x:v>
+        <x:v>51 986 185 776</x:v>
       </x:c>
       <x:c r="J120" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K120" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L120" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M120" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N120" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="O120" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="P120" t="str">
-        <x:v>22/08/2026</x:v>
+        <x:v>18/07/2026</x:v>
       </x:c>
       <x:c r="Q120" t="n">
-        <x:v>579</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R120" t="n">
-        <x:v>579</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S120" t="n">
         <x:v>0</x:v>
@@ -11248,55 +11476,55 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B121" t="str">
-        <x:v>Marcela Noblecilla</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="C121" t="str">
-        <x:v>998678319</x:v>
+        <x:v>940219366</x:v>
       </x:c>
       <x:c r="D121" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E121" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F121" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G121" t="str">
-        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="H121" t="str">
-        <x:v>10058157</x:v>
+        <x:v>45267059</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>51998 678 319</x:v>
+        <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J121" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L121" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M121" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N121" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>06/07/2026</x:v>
       </x:c>
       <x:c r="O121" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>06/07/2026</x:v>
       </x:c>
       <x:c r="P121" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="Q121" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R121" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S121" t="n">
         <x:v>0</x:v>
@@ -11310,61 +11538,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B122" t="str">
-        <x:v>Marcela Noblecilla</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="C122" t="str">
-        <x:v>998678319</x:v>
+        <x:v>940219366</x:v>
       </x:c>
       <x:c r="D122" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E122" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F122" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G122" t="str">
-        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="H122" t="str">
-        <x:v>10058157</x:v>
+        <x:v>45267059</x:v>
       </x:c>
       <x:c r="I122" t="str">
-        <x:v>51998 678 319</x:v>
+        <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J122" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L122" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M122" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N122" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="O122" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="P122" t="str">
-        <x:v>07/08/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="Q122" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R122" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S122" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T122" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -11372,28 +11600,28 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B123" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="C123" t="str">
-        <x:v>992978868</x:v>
+        <x:v>940219366</x:v>
       </x:c>
       <x:c r="D123" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E123" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F123" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G123" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="H123" t="str">
-        <x:v>09339021</x:v>
+        <x:v>45267059</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>51992978868</x:v>
+        <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J123" t="str">
         <x:v>Renovacion</x:v>
@@ -11402,31 +11630,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L123" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M123" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N123" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="O123" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="P123" t="str">
-        <x:v>25/07/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="Q123" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R123" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S123" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T123" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -11434,28 +11662,28 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B124" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="C124" t="str">
-        <x:v>992978868</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="D124" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E124" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F124" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G124" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="H124" t="str">
-        <x:v>09339021</x:v>
+        <x:v>009248655</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>51992978868</x:v>
+        <x:v>51941568528</x:v>
       </x:c>
       <x:c r="J124" t="str">
         <x:v>Nuevo</x:v>
@@ -11470,13 +11698,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N124" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>13/07/2026</x:v>
       </x:c>
       <x:c r="O124" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>13/07/2026</x:v>
       </x:c>
       <x:c r="P124" t="str">
-        <x:v>08/08/2026</x:v>
+        <x:v>28/07/2026</x:v>
       </x:c>
       <x:c r="Q124" t="n">
         <x:v>1000</x:v>
@@ -11496,28 +11724,28 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B125" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="C125" t="str">
-        <x:v>992978868</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="D125" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E125" t="str">
-        <x:v>DM</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F125" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G125" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="H125" t="str">
-        <x:v>09339021</x:v>
+        <x:v>009248655</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>51992978868</x:v>
+        <x:v>51941568528</x:v>
       </x:c>
       <x:c r="J125" t="str">
         <x:v>Renovacion</x:v>
@@ -11526,25 +11754,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L125" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M125" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N125" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O125" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P125" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>22/08/2026</x:v>
       </x:c>
       <x:c r="Q125" t="n">
-        <x:v>2219</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R125" t="n">
-        <x:v>2219</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S125" t="n">
         <x:v>0</x:v>
@@ -11558,55 +11786,55 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B126" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Marcela Noblecilla</x:v>
       </x:c>
       <x:c r="C126" t="str">
-        <x:v>997512348</x:v>
+        <x:v>998678319</x:v>
       </x:c>
       <x:c r="D126" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E126" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F126" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G126" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
       </x:c>
       <x:c r="H126" t="str">
-        <x:v>09673494</x:v>
+        <x:v>10058157</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>997 512 348</x:v>
+        <x:v>51998 678 319</x:v>
       </x:c>
       <x:c r="J126" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L126" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M126" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N126" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O126" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P126" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="Q126" t="n">
-        <x:v>2219</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R126" t="n">
-        <x:v>2219</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S126" t="n">
         <x:v>0</x:v>
@@ -11620,28 +11848,28 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B127" t="str">
-        <x:v>Lylian Leon</x:v>
+        <x:v>Marcela Noblecilla</x:v>
       </x:c>
       <x:c r="C127" t="str">
-        <x:v>996500716</x:v>
+        <x:v>998678319</x:v>
       </x:c>
       <x:c r="D127" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E127" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F127" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G127" t="str">
-        <x:v>Lylian León</x:v>
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
       </x:c>
       <x:c r="H127" t="str">
-        <x:v>07619479</x:v>
+        <x:v>10058157</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>996500716</x:v>
+        <x:v>51998 678 319</x:v>
       </x:c>
       <x:c r="J127" t="str">
         <x:v>Nuevo</x:v>
@@ -11656,13 +11884,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N127" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O127" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P127" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="Q127" t="n">
         <x:v>1000</x:v>
@@ -11679,73 +11907,75 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B128" t="str">
-        <x:v>Karina Saavedra</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="C128" t="str">
-        <x:v>984609397</x:v>
+        <x:v>992978868</x:v>
       </x:c>
       <x:c r="D128" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E128" t="str"/>
+      <x:c r="E128" t="str">
+        <x:v>DM</x:v>
+      </x:c>
       <x:c r="F128" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G128" t="str">
-        <x:v>Karina Saavedra Zarria</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="H128" t="str">
-        <x:v>07628122</x:v>
+        <x:v>09339021</x:v>
       </x:c>
       <x:c r="I128" t="str">
-        <x:v>51984609397</x:v>
+        <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J128" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K128" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L128" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M128" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N128" t="str">
-        <x:v>10/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="O128" t="str">
-        <x:v>10/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P128" t="str">
-        <x:v>25/08/2026</x:v>
+        <x:v>25/07/2026</x:v>
       </x:c>
       <x:c r="Q128" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R128" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S128" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T128" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>SIN VENDEDOR</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B129" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="C129" t="str">
-        <x:v>977648321</x:v>
+        <x:v>992978868</x:v>
       </x:c>
       <x:c r="D129" t="n">
         <x:v>1900</x:v>
@@ -11757,57 +11987,57 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G129" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="H129" t="str">
-        <x:v>40154559</x:v>
+        <x:v>09339021</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J129" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L129" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M129" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N129" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="O129" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P129" t="str">
-        <x:v>28/08/2026</x:v>
+        <x:v>08/08/2026</x:v>
       </x:c>
       <x:c r="Q129" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R129" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S129" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T129" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B130" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="C130" t="str">
-        <x:v>977648321</x:v>
+        <x:v>992978868</x:v>
       </x:c>
       <x:c r="D130" t="n">
         <x:v>1900</x:v>
@@ -11819,13 +12049,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G130" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="H130" t="str">
-        <x:v>40154559</x:v>
+        <x:v>09339021</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>Renovacion</x:v>
@@ -11834,60 +12064,60 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L130" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M130" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N130" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="O130" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="P130" t="str">
-        <x:v>13/08/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q130" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R130" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S130" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T130" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B131" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="C131" t="str">
-        <x:v>977648321</x:v>
+        <x:v>997512348</x:v>
       </x:c>
       <x:c r="D131" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E131" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F131" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G131" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="H131" t="str">
-        <x:v>40154559</x:v>
+        <x:v>09673494</x:v>
       </x:c>
       <x:c r="I131" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J131" t="str">
         <x:v>Nuevo</x:v>
@@ -11899,22 +12129,22 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M131" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N131" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="O131" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="P131" t="str">
-        <x:v>27/08/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q131" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R131" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S131" t="n">
         <x:v>0</x:v>
@@ -11925,31 +12155,31 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B132" t="str">
-        <x:v>Jeanne Goncalvez</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="C132" t="str">
-        <x:v>2022790015</x:v>
+        <x:v>997512348</x:v>
       </x:c>
       <x:c r="D132" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E132" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F132" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>JEANNE GONCALVEZ</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="H132" t="str">
-        <x:v>20230943</x:v>
+        <x:v>09673494</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>51+1 (202) 279-0015</x:v>
+        <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J132" t="str">
         <x:v>Renovacion</x:v>
@@ -11958,25 +12188,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L132" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M132" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N132" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="O132" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="P132" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>26/09/2026</x:v>
       </x:c>
       <x:c r="Q132" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R132" t="n">
-        <x:v>900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S132" t="n">
         <x:v>0</x:v>
@@ -11987,37 +12217,37 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B133" t="str">
-        <x:v>Jeanne Goncalvez</x:v>
+        <x:v>Lylian Leon</x:v>
       </x:c>
       <x:c r="C133" t="str">
-        <x:v>2022790015</x:v>
+        <x:v>996500716</x:v>
       </x:c>
       <x:c r="D133" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E133" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F133" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G133" t="str">
-        <x:v>JEANNE GONCALVEZ</x:v>
+        <x:v>Lylian León</x:v>
       </x:c>
       <x:c r="H133" t="str">
-        <x:v>20230943</x:v>
+        <x:v>07619479</x:v>
       </x:c>
       <x:c r="I133" t="str">
-        <x:v>51+1 (202) 279-0015</x:v>
+        <x:v>996500716</x:v>
       </x:c>
       <x:c r="J133" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L133" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -12026,13 +12256,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N133" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="O133" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="P133" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>15/08/2026</x:v>
       </x:c>
       <x:c r="Q133" t="n">
         <x:v>1000</x:v>
@@ -12044,7 +12274,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T133" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -12052,61 +12282,59 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B134" t="str">
-        <x:v>Eduardo Franca</x:v>
+        <x:v>Karina Saavedra</x:v>
       </x:c>
       <x:c r="C134" t="str">
-        <x:v>2025600320</x:v>
+        <x:v>984609397</x:v>
       </x:c>
       <x:c r="D134" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E134" t="str">
-        <x:v>Mirko</x:v>
-      </x:c>
+      <x:c r="E134" t="str"/>
       <x:c r="F134" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G134" t="str">
-        <x:v>EDUARDO FRANCA</x:v>
+        <x:v>Karina Saavedra Zarria</x:v>
       </x:c>
       <x:c r="H134" t="str">
-        <x:v>20230623</x:v>
+        <x:v>07628122</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>51+1 (202) 560-0320</x:v>
+        <x:v>51984609397</x:v>
       </x:c>
       <x:c r="J134" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L134" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M134" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N134" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>10/08/2026</x:v>
       </x:c>
       <x:c r="O134" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>10/08/2026</x:v>
       </x:c>
       <x:c r="P134" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>25/08/2026</x:v>
       </x:c>
       <x:c r="Q134" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R134" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S134" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T134" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -12114,55 +12342,55 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B135" t="str">
-        <x:v>Eduardo Franca</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C135" t="str">
-        <x:v>2025600320</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D135" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E135" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F135" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G135" t="str">
-        <x:v>EDUARDO FRANCA</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H135" t="str">
-        <x:v>20230623</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>51+1 (202) 560-0320</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J135" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K135" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L135" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M135" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N135" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O135" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P135" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>28/08/2026</x:v>
       </x:c>
       <x:c r="Q135" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R135" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S135" t="n">
         <x:v>0</x:v>
@@ -12176,53 +12404,55 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B136" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C136" t="str">
-        <x:v>989174565</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D136" t="n">
-        <x:v>2884</x:v>
-      </x:c>
-      <x:c r="E136" t="str"/>
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>DM</x:v>
+      </x:c>
       <x:c r="F136" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G136" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H136" t="str">
-        <x:v>09752091</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I136" t="str">
-        <x:v>51989174565</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J136" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L136" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M136" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N136" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O136" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P136" t="str">
-        <x:v>17/09/2026</x:v>
+        <x:v>13/08/2026</x:v>
       </x:c>
       <x:c r="Q136" t="n">
-        <x:v>2884</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R136" t="n">
-        <x:v>2884</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S136" t="n">
         <x:v>0</x:v>
@@ -12236,32 +12466,34 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B137" t="str">
-        <x:v>Maribel Toledo</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C137" t="str">
-        <x:v>949604263</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D137" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E137" t="str"/>
+      <x:c r="E137" t="str">
+        <x:v>DM</x:v>
+      </x:c>
       <x:c r="F137" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G137" t="str">
-        <x:v>MARIBEL TOLEDO</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H137" t="str">
-        <x:v>10477277</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I137" t="str">
-        <x:v>51949604263</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J137" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K137" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L137" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -12270,13 +12502,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N137" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O137" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P137" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="Q137" t="n">
         <x:v>1000</x:v>
@@ -12296,26 +12528,28 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B138" t="str">
-        <x:v>Maribel Toledo</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C138" t="str">
-        <x:v>949604263</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D138" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E138" t="str"/>
+      <x:c r="E138" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F138" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G138" t="str">
-        <x:v>MARIBEL TOLEDO</x:v>
+        <x:v>JEANNE GONCALVEZ</x:v>
       </x:c>
       <x:c r="H138" t="str">
-        <x:v>10477277</x:v>
+        <x:v>20230943</x:v>
       </x:c>
       <x:c r="I138" t="str">
-        <x:v>51949604263</x:v>
+        <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J138" t="str">
         <x:v>Renovacion</x:v>
@@ -12330,13 +12564,13 @@
         <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N138" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O138" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P138" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>15/08/2026</x:v>
       </x:c>
       <x:c r="Q138" t="n">
         <x:v>900</x:v>
@@ -12356,59 +12590,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B139" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C139" t="str">
-        <x:v>997527485</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D139" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E139" t="str"/>
+      <x:c r="E139" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F139" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G139" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>JEANNE GONCALVEZ</x:v>
       </x:c>
       <x:c r="H139" t="str">
-        <x:v>997527485</x:v>
+        <x:v>20230943</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>10545751</x:v>
+        <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J139" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L139" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M139" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N139" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O139" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P139" t="str">
-        <x:v>20/08/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q139" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R139" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S139" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T139" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -12416,58 +12652,856 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B140" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C140" t="str">
-        <x:v>997527485</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D140" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E140" t="str"/>
+      <x:c r="E140" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F140" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>JEANNE GONCALVEZ</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>20230943</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>51+1 (202) 279-0015</x:v>
+      </x:c>
+      <x:c r="J140" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L140" t="str">
+        <x:v>MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>26/08/2026</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="P140" t="str">
+        <x:v>02/10/2026</x:v>
+      </x:c>
+      <x:c r="Q140" t="n">
+        <x:v>1385</x:v>
+      </x:c>
+      <x:c r="R140" t="n">
+        <x:v>1385</x:v>
+      </x:c>
+      <x:c r="S140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T140" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D141" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J141" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L141" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O141" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P141" t="str">
+        <x:v>15/08/2026</x:v>
+      </x:c>
+      <x:c r="Q141" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R141" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T141" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D142" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H142" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J142" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L142" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="O142" t="str">
+        <x:v>14/08/2026</x:v>
+      </x:c>
+      <x:c r="P142" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="Q142" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R142" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T142" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>Eduardo Franca</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>2025600320</x:v>
+      </x:c>
+      <x:c r="D143" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>EDUARDO FRANCA</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>20230623</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>51+1 (202) 560-0320</x:v>
+      </x:c>
+      <x:c r="J143" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L143" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>26/08/2026</x:v>
+      </x:c>
+      <x:c r="O143" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="P143" t="str">
+        <x:v>02/10/2026</x:v>
+      </x:c>
+      <x:c r="Q143" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="R143" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="S143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T143" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>989174565</x:v>
+      </x:c>
+      <x:c r="D144" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="E144" t="str"/>
+      <x:c r="F144" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>Jacqueline Banchero Herrera</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>09752091</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>51989174565</x:v>
+      </x:c>
+      <x:c r="J144" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L144" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>1 mes</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O144" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P144" t="str">
+        <x:v>17/09/2026</x:v>
+      </x:c>
+      <x:c r="Q144" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="R144" t="n">
+        <x:v>2884</x:v>
+      </x:c>
+      <x:c r="S144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T144" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>Maribel Toledo</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>949604263</x:v>
+      </x:c>
+      <x:c r="D145" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E145" t="str"/>
+      <x:c r="F145" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>MARIBEL TOLEDO</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>10477277</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>51949604263</x:v>
+      </x:c>
+      <x:c r="J145" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L145" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O145" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P145" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="Q145" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R145" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T145" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>Maribel Toledo</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>949604263</x:v>
+      </x:c>
+      <x:c r="D146" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E146" t="str"/>
+      <x:c r="F146" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>MARIBEL TOLEDO</x:v>
+      </x:c>
+      <x:c r="H146" t="str">
+        <x:v>10477277</x:v>
+      </x:c>
+      <x:c r="I146" t="str">
+        <x:v>51949604263</x:v>
+      </x:c>
+      <x:c r="J146" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K146" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L146" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M146" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N146" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O146" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P146" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="Q146" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R146" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T146" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="D147" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E147" t="str"/>
+      <x:c r="F147" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
-      <x:c r="G140" t="str">
+      <x:c r="G147" t="str">
         <x:v>Silvina Gorbitz</x:v>
       </x:c>
-      <x:c r="H140" t="str">
+      <x:c r="H147" t="str">
         <x:v>997527485</x:v>
       </x:c>
-      <x:c r="I140" t="str">
+      <x:c r="I147" t="str">
         <x:v>10545751</x:v>
       </x:c>
-      <x:c r="J140" t="str">
+      <x:c r="J147" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K147" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L147" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M147" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N147" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="O147" t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c r="P147" t="str">
+        <x:v>20/08/2026</x:v>
+      </x:c>
+      <x:c r="Q147" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R147" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T147" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="D148" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E148" t="str"/>
+      <x:c r="F148" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>Silvina Gorbitz</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>997527485</x:v>
+      </x:c>
+      <x:c r="I148" t="str">
+        <x:v>10545751</x:v>
+      </x:c>
+      <x:c r="J148" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
-      <x:c r="K140" t="str">
+      <x:c r="K148" t="str">
         <x:v>Digital</x:v>
       </x:c>
-      <x:c r="L140" t="str">
+      <x:c r="L148" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
-      <x:c r="M140" t="str">
+      <x:c r="M148" t="str">
         <x:v>15 dias</x:v>
       </x:c>
-      <x:c r="N140" t="str">
+      <x:c r="N148" t="str">
         <x:v>19/08/2026</x:v>
       </x:c>
-      <x:c r="O140" t="str">
+      <x:c r="O148" t="str">
         <x:v>19/08/2026</x:v>
       </x:c>
-      <x:c r="P140" t="str">
+      <x:c r="P148" t="str">
         <x:v>03/09/2026</x:v>
       </x:c>
-      <x:c r="Q140" t="n">
+      <x:c r="Q148" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="R140" t="n">
+      <x:c r="R148" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="S140" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T140" t="str">
+      <x:c r="S148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T148" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>Sandra Contreras</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>948067720</x:v>
+      </x:c>
+      <x:c r="D149" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>SANDRA CONTRERAS</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>07465701</x:v>
+      </x:c>
+      <x:c r="I149" t="str">
+        <x:v>51948706868</x:v>
+      </x:c>
+      <x:c r="J149" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K149" t="str">
+        <x:v>Walk in</x:v>
+      </x:c>
+      <x:c r="L149" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M149" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N149" t="str">
+        <x:v>24/08/2026</x:v>
+      </x:c>
+      <x:c r="O149" t="str">
+        <x:v>24/08/2026</x:v>
+      </x:c>
+      <x:c r="P149" t="str">
+        <x:v>08/09/2026</x:v>
+      </x:c>
+      <x:c r="Q149" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R149" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T149" t="str">
+        <x:v>mafervta</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>Federico Leon</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>948687720</x:v>
+      </x:c>
+      <x:c r="D150" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>Federico Leon</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>07869853</x:v>
+      </x:c>
+      <x:c r="I150" t="str">
+        <x:v>51994687720</x:v>
+      </x:c>
+      <x:c r="J150" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K150" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L150" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M150" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N150" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="O150" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="P150" t="str">
+        <x:v>09/09/2026</x:v>
+      </x:c>
+      <x:c r="Q150" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R150" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T150" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>Daniela Door</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>997959393</x:v>
+      </x:c>
+      <x:c r="D151" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F151" t="str">
+        <x:v>Nombre exacto</x:v>
+      </x:c>
+      <x:c r="G151" t="str">
+        <x:v>Daniela Door</x:v>
+      </x:c>
+      <x:c r="H151" t="str">
+        <x:v>07761819</x:v>
+      </x:c>
+      <x:c r="I151" t="str">
+        <x:v>51997595393</x:v>
+      </x:c>
+      <x:c r="J151" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K151" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L151" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M151" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N151" t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c r="O151" t="str">
+        <x:v>28/08/2026</x:v>
+      </x:c>
+      <x:c r="P151" t="str">
+        <x:v>12/09/2026</x:v>
+      </x:c>
+      <x:c r="Q151" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R151" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T151" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>968765284</x:v>
+      </x:c>
+      <x:c r="D152" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F152" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G152" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="H152" t="str">
+        <x:v>21533929</x:v>
+      </x:c>
+      <x:c r="I152" t="str">
+        <x:v>51968 765 284</x:v>
+      </x:c>
+      <x:c r="J152" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K152" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L152" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M152" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N152" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="O152" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="P152" t="str">
+        <x:v>30/08/2026</x:v>
+      </x:c>
+      <x:c r="Q152" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R152" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T152" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>Agosto 2026</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>968765284</x:v>
+      </x:c>
+      <x:c r="D153" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>DM</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>Mariela Espino</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>21533929</x:v>
+      </x:c>
+      <x:c r="I153" t="str">
+        <x:v>51968 765 284</x:v>
+      </x:c>
+      <x:c r="J153" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K153" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L153" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M153" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N153" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="O153" t="str">
+        <x:v>29/08/2026</x:v>
+      </x:c>
+      <x:c r="P153" t="str">
+        <x:v>13/09/2026</x:v>
+      </x:c>
+      <x:c r="Q153" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R153" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T153" t="str">
         <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
